--- a/BackEnd/dimensao_BrasileiraoB_completo.xlsx
+++ b/BackEnd/dimensao_BrasileiraoB_completo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G387"/>
+  <dimension ref="A1:I387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,17 +439,27 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>ID_Casa</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Gols_Casa</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Gols_Fora</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Time_Fora</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ID_Fora</t>
         </is>
       </c>
     </row>
@@ -471,15 +481,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>1960</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>Amazonas FC</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>336664</v>
       </c>
     </row>
     <row r="3">
@@ -500,15 +516,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>1984</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Operário-PR</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>39634</v>
       </c>
     </row>
     <row r="4">
@@ -529,15 +551,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>1997</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="5">
@@ -558,15 +586,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>22032</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>21845</v>
       </c>
     </row>
     <row r="6">
@@ -587,15 +621,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>1982</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Vila Nova FC</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="7">
@@ -616,15 +656,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>1973</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Botafogo-SP</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1979</v>
       </c>
     </row>
     <row r="8">
@@ -645,15 +691,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>35285</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="9">
@@ -674,15 +726,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>6982</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Cuiabá</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49202</v>
       </c>
     </row>
     <row r="10">
@@ -703,15 +761,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>7315</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>Grêmio Novorizontino</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>135514</v>
       </c>
     </row>
     <row r="11">
@@ -732,15 +796,21 @@
         </is>
       </c>
       <c r="E11" t="n">
+        <v>7314</v>
+      </c>
+      <c r="F11" t="n">
         <v>4</v>
       </c>
-      <c r="F11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="12">
@@ -761,15 +831,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1967</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="13">
@@ -790,15 +866,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>49202</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>7315</v>
       </c>
     </row>
     <row r="14">
@@ -819,15 +901,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>21845</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1982</v>
       </c>
     </row>
     <row r="15">
@@ -848,15 +936,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2021</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>Paysandu SC</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1997</v>
       </c>
     </row>
     <row r="16">
@@ -877,15 +971,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>336664</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="17">
@@ -906,15 +1006,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>135514</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6982</v>
       </c>
     </row>
     <row r="18">
@@ -935,15 +1041,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>39634</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="19">
@@ -964,15 +1076,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>342775</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="20">
@@ -993,15 +1111,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>2012</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="21">
@@ -1022,15 +1146,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>1979</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>Atlético Goianiense</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>7314</v>
       </c>
     </row>
     <row r="22">
@@ -1051,15 +1181,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>49202</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="23">
@@ -1080,15 +1216,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>7315</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>Operário-PR</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>39634</v>
       </c>
     </row>
     <row r="24">
@@ -1109,15 +1251,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1997</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
-      </c>
-      <c r="G24" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>21845</v>
       </c>
     </row>
     <row r="25">
@@ -1138,15 +1286,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1982</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>Grêmio Novorizontino</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>135514</v>
       </c>
     </row>
     <row r="26">
@@ -1167,15 +1321,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>1960</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>Vila Nova FC</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="27">
@@ -1196,15 +1356,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>1979</v>
       </c>
       <c r="F27" t="n">
         <v>2</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="28">
@@ -1225,15 +1391,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>22032</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>6982</v>
       </c>
     </row>
     <row r="29">
@@ -1254,15 +1426,21 @@
         </is>
       </c>
       <c r="E29" t="n">
+        <v>1984</v>
+      </c>
+      <c r="F29" t="n">
         <v>4</v>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="30">
@@ -1283,15 +1461,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>35285</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>Atlético Goianiense</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>7314</v>
       </c>
     </row>
     <row r="31">
@@ -1312,15 +1496,21 @@
         </is>
       </c>
       <c r="E31" t="n">
+        <v>1973</v>
+      </c>
+      <c r="F31" t="n">
         <v>3</v>
       </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>Amazonas FC</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>336664</v>
       </c>
     </row>
     <row r="32">
@@ -1341,15 +1531,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>39634</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>Paysandu SC</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1997</v>
       </c>
     </row>
     <row r="33">
@@ -1370,15 +1566,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>2021</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>Botafogo-SP</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1979</v>
       </c>
     </row>
     <row r="34">
@@ -1399,15 +1601,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>21845</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="35">
@@ -1428,15 +1636,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>1967</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="36">
@@ -1457,15 +1671,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>1973</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="37">
@@ -1486,15 +1706,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>336664</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
-      </c>
-      <c r="G37" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>7315</v>
       </c>
     </row>
     <row r="38">
@@ -1515,15 +1741,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>135514</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="39">
@@ -1544,15 +1776,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>2012</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>1982</v>
       </c>
     </row>
     <row r="40">
@@ -1573,15 +1811,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>7314</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>Cuiabá</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49202</v>
       </c>
     </row>
     <row r="41">
@@ -1602,15 +1846,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>6982</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="42">
@@ -1631,15 +1881,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>135514</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="43">
@@ -1660,15 +1916,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>1984</v>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="44">
@@ -1689,15 +1951,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>2021</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>21845</v>
       </c>
     </row>
     <row r="45">
@@ -1718,15 +1986,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>1982</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>Operário-PR</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>39634</v>
       </c>
     </row>
     <row r="46">
@@ -1747,15 +2021,21 @@
         </is>
       </c>
       <c r="E46" t="n">
+        <v>7315</v>
+      </c>
+      <c r="F46" t="n">
         <v>3</v>
       </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="47">
@@ -1776,15 +2056,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>342775</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>6982</v>
       </c>
     </row>
     <row r="48">
@@ -1805,15 +2091,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>336664</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>Atlético Goianiense</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>7314</v>
       </c>
     </row>
     <row r="49">
@@ -1834,15 +2126,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>1997</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="50">
@@ -1863,15 +2161,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>49202</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="51">
@@ -1892,15 +2196,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1979</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="52">
@@ -1921,15 +2231,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>35285</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>1982</v>
       </c>
     </row>
     <row r="53">
@@ -1950,15 +2266,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>2012</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
         <is>
           <t>Amazonas FC</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>336664</v>
       </c>
     </row>
     <row r="54">
@@ -1979,15 +2301,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>6982</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>Paysandu SC</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>1997</v>
       </c>
     </row>
     <row r="55">
@@ -2008,15 +2336,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>7314</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr">
         <is>
           <t>Grêmio Novorizontino</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>135514</v>
       </c>
     </row>
     <row r="56">
@@ -2037,15 +2371,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>1967</v>
       </c>
       <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
         <v>4</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Botafogo-SP</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>1979</v>
       </c>
     </row>
     <row r="57">
@@ -2066,15 +2406,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>21845</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="58">
@@ -2095,15 +2441,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>39634</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="59">
@@ -2124,15 +2476,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>1960</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>7315</v>
       </c>
     </row>
     <row r="60">
@@ -2153,15 +2511,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>22032</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>Cuiabá</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49202</v>
       </c>
     </row>
     <row r="61">
@@ -2182,15 +2546,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>342775</v>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" t="inlineStr">
         <is>
           <t>Vila Nova FC</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="62">
@@ -2211,15 +2581,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>1967</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>21845</v>
       </c>
     </row>
     <row r="63">
@@ -2240,15 +2616,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>7315</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="inlineStr">
         <is>
           <t>Atlético Goianiense</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>7314</v>
       </c>
     </row>
     <row r="64">
@@ -2269,15 +2651,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>1960</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>1982</v>
       </c>
     </row>
     <row r="65">
@@ -2298,15 +2686,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1984</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>6982</v>
       </c>
     </row>
     <row r="66">
@@ -2327,15 +2721,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>49202</v>
       </c>
       <c r="F66" t="n">
+        <v>2</v>
+      </c>
+      <c r="G66" t="n">
         <v>3</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>Operário-PR</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>39634</v>
       </c>
     </row>
     <row r="67">
@@ -2356,15 +2756,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>135514</v>
       </c>
       <c r="F67" t="n">
         <v>2</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" t="n">
+        <v>2</v>
+      </c>
+      <c r="H67" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="68">
@@ -2385,15 +2791,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>1979</v>
       </c>
       <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
         <v>3</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="69">
@@ -2414,15 +2826,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>336664</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="70">
@@ -2443,15 +2861,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>2012</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="inlineStr">
         <is>
           <t>Vila Nova FC</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="71">
@@ -2472,15 +2896,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>1973</v>
       </c>
       <c r="F71" t="n">
         <v>2</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" t="n">
+        <v>2</v>
+      </c>
+      <c r="H71" t="inlineStr">
         <is>
           <t>Paysandu SC</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>1997</v>
       </c>
     </row>
     <row r="72">
@@ -2501,15 +2931,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>35285</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>7315</v>
       </c>
     </row>
     <row r="73">
@@ -2530,15 +2966,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>21845</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="inlineStr">
         <is>
           <t>Cuiabá</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49202</v>
       </c>
     </row>
     <row r="74">
@@ -2559,15 +3001,21 @@
         </is>
       </c>
       <c r="E74" t="n">
+        <v>39634</v>
+      </c>
+      <c r="F74" t="n">
         <v>3</v>
       </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="inlineStr">
         <is>
           <t>Botafogo-SP</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>1979</v>
       </c>
     </row>
     <row r="75">
@@ -2588,15 +3036,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>2021</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="76">
@@ -2617,15 +3071,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>342775</v>
       </c>
       <c r="F76" t="n">
-        <v>2</v>
-      </c>
-      <c r="G76" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" t="inlineStr">
         <is>
           <t>Grêmio Novorizontino</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>135514</v>
       </c>
     </row>
     <row r="77">
@@ -2646,15 +3106,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>7314</v>
       </c>
       <c r="F77" t="n">
         <v>1</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="78">
@@ -2675,15 +3141,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>22032</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="79">
@@ -2704,15 +3176,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>1997</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="80">
@@ -2733,15 +3211,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>6982</v>
       </c>
       <c r="F80" t="n">
         <v>1</v>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="inlineStr">
         <is>
           <t>Amazonas FC</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>336664</v>
       </c>
     </row>
     <row r="81">
@@ -2762,15 +3246,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>1982</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="82">
@@ -2791,15 +3281,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>1960</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="83">
@@ -2820,15 +3316,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>1967</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="84">
@@ -2849,15 +3351,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>2012</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>6982</v>
       </c>
     </row>
     <row r="85">
@@ -2878,15 +3386,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2</v>
+        <v>7315</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>21845</v>
       </c>
     </row>
     <row r="86">
@@ -2907,15 +3421,21 @@
         </is>
       </c>
       <c r="E86" t="n">
+        <v>135514</v>
+      </c>
+      <c r="F86" t="n">
         <v>3</v>
       </c>
-      <c r="F86" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="inlineStr">
         <is>
           <t>Paysandu SC</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>1997</v>
       </c>
     </row>
     <row r="87">
@@ -2936,15 +3456,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>336664</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t>Operário-PR</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>39634</v>
       </c>
     </row>
     <row r="88">
@@ -2965,15 +3491,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1984</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>1982</v>
       </c>
     </row>
     <row r="89">
@@ -2994,15 +3526,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>1979</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="90">
@@ -3023,15 +3561,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>49202</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="inlineStr">
         <is>
           <t>Vila Nova FC</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="91">
@@ -3052,15 +3596,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>1973</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="inlineStr">
         <is>
           <t>Atlético Goianiense</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>7314</v>
       </c>
     </row>
     <row r="92">
@@ -3081,15 +3631,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>35285</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="inlineStr">
         <is>
           <t>Botafogo-SP</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>1979</v>
       </c>
     </row>
     <row r="93">
@@ -3110,15 +3666,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>2021</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="inlineStr">
         <is>
           <t>Grêmio Novorizontino</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>135514</v>
       </c>
     </row>
     <row r="94">
@@ -3139,15 +3701,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>1982</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>7315</v>
       </c>
     </row>
     <row r="95">
@@ -3168,15 +3736,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>7314</v>
       </c>
       <c r="F95" t="n">
-        <v>2</v>
-      </c>
-      <c r="G95" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2</v>
+      </c>
+      <c r="H95" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="96">
@@ -3197,15 +3771,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>342775</v>
       </c>
       <c r="F96" t="n">
-        <v>2</v>
-      </c>
-      <c r="G96" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>2</v>
+      </c>
+      <c r="H96" t="inlineStr">
         <is>
           <t>Cuiabá</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49202</v>
       </c>
     </row>
     <row r="97">
@@ -3226,15 +3806,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2</v>
+        <v>39634</v>
       </c>
       <c r="F97" t="n">
         <v>2</v>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G97" t="n">
+        <v>2</v>
+      </c>
+      <c r="H97" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I97" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="98">
@@ -3255,15 +3841,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>22032</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I98" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="99">
@@ -3284,15 +3876,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>6982</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
+      </c>
+      <c r="I99" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="100">
@@ -3313,15 +3911,21 @@
         </is>
       </c>
       <c r="E100" t="n">
+        <v>21845</v>
+      </c>
+      <c r="F100" t="n">
         <v>4</v>
       </c>
-      <c r="F100" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" t="inlineStr">
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="inlineStr">
         <is>
           <t>Amazonas FC</t>
         </is>
+      </c>
+      <c r="I100" t="n">
+        <v>336664</v>
       </c>
     </row>
     <row r="101">
@@ -3342,15 +3946,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>1997</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
-      </c>
-      <c r="G101" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I101" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="102">
@@ -3371,15 +3981,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>1979</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
+      </c>
+      <c r="I102" t="n">
+        <v>1982</v>
       </c>
     </row>
     <row r="103">
@@ -3400,15 +4016,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1</v>
+        <v>135514</v>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
+      </c>
+      <c r="I103" t="n">
+        <v>21845</v>
       </c>
     </row>
     <row r="104">
@@ -3429,15 +4051,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1</v>
+        <v>49202</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="inlineStr">
         <is>
           <t>Paysandu SC</t>
         </is>
+      </c>
+      <c r="I104" t="n">
+        <v>1997</v>
       </c>
     </row>
     <row r="105">
@@ -3458,15 +4086,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1</v>
+        <v>1973</v>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
-      </c>
-      <c r="G105" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G105" t="n">
+        <v>2</v>
+      </c>
+      <c r="H105" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I105" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="106">
@@ -3487,15 +4121,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1</v>
+        <v>7315</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I106" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="107">
@@ -3516,15 +4156,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2</v>
+        <v>1960</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
+      </c>
+      <c r="I107" t="n">
+        <v>6982</v>
       </c>
     </row>
     <row r="108">
@@ -3545,15 +4191,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>1967</v>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
-      </c>
-      <c r="G108" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" t="inlineStr">
         <is>
           <t>Atlético Goianiense</t>
         </is>
+      </c>
+      <c r="I108" t="n">
+        <v>7314</v>
       </c>
     </row>
     <row r="109">
@@ -3574,15 +4226,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2</v>
+        <v>2012</v>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
-      </c>
-      <c r="G109" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" t="inlineStr">
         <is>
           <t>Operário-PR</t>
         </is>
+      </c>
+      <c r="I109" t="n">
+        <v>39634</v>
       </c>
     </row>
     <row r="110">
@@ -3603,15 +4261,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1</v>
+        <v>1984</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="inlineStr">
         <is>
           <t>Vila Nova FC</t>
         </is>
+      </c>
+      <c r="I110" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="111">
@@ -3632,15 +4296,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1</v>
+        <v>336664</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I111" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="112">
@@ -3661,15 +4331,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>2021</v>
       </c>
       <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
         <v>3</v>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="H112" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
+      </c>
+      <c r="I112" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="113">
@@ -3690,15 +4366,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>1997</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="inlineStr">
         <is>
           <t>Botafogo-SP</t>
         </is>
+      </c>
+      <c r="I113" t="n">
+        <v>1979</v>
       </c>
     </row>
     <row r="114">
@@ -3719,15 +4401,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2</v>
+        <v>22032</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
+      </c>
+      <c r="I114" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="115">
@@ -3748,15 +4436,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2</v>
+        <v>1967</v>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
-      </c>
-      <c r="G115" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I115" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="116">
@@ -3777,15 +4471,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2</v>
+        <v>342775</v>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
-      </c>
-      <c r="G116" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" t="inlineStr">
         <is>
           <t>Operário-PR</t>
         </is>
+      </c>
+      <c r="I116" t="n">
+        <v>39634</v>
       </c>
     </row>
     <row r="117">
@@ -3806,15 +4506,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>7314</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
+      </c>
+      <c r="I117" t="n">
+        <v>1982</v>
       </c>
     </row>
     <row r="118">
@@ -3835,15 +4541,21 @@
         </is>
       </c>
       <c r="E118" t="n">
+        <v>135514</v>
+      </c>
+      <c r="F118" t="n">
         <v>3</v>
       </c>
-      <c r="F118" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" t="inlineStr">
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="inlineStr">
         <is>
           <t>Cuiabá</t>
         </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49202</v>
       </c>
     </row>
     <row r="119">
@@ -3864,15 +4576,21 @@
         </is>
       </c>
       <c r="E119" t="n">
+        <v>1984</v>
+      </c>
+      <c r="F119" t="n">
         <v>3</v>
       </c>
-      <c r="F119" t="n">
-        <v>2</v>
-      </c>
-      <c r="G119" t="inlineStr">
+      <c r="G119" t="n">
+        <v>2</v>
+      </c>
+      <c r="H119" t="inlineStr">
         <is>
           <t>Amazonas FC</t>
         </is>
+      </c>
+      <c r="I119" t="n">
+        <v>336664</v>
       </c>
     </row>
     <row r="120">
@@ -3893,15 +4611,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2</v>
+        <v>21845</v>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
-      </c>
-      <c r="G120" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I120" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="121">
@@ -3922,15 +4646,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1</v>
+        <v>6982</v>
       </c>
       <c r="F121" t="n">
         <v>1</v>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G121" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
+      </c>
+      <c r="I121" t="n">
+        <v>7315</v>
       </c>
     </row>
     <row r="122">
@@ -3951,15 +4681,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1</v>
+        <v>1979</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
-      </c>
-      <c r="G122" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
+      </c>
+      <c r="I122" t="n">
+        <v>21845</v>
       </c>
     </row>
     <row r="123">
@@ -3980,15 +4716,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1</v>
+        <v>1973</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G123" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I123" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="124">
@@ -4009,15 +4751,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1</v>
+        <v>7315</v>
       </c>
       <c r="F124" t="n">
-        <v>2</v>
-      </c>
-      <c r="G124" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2</v>
+      </c>
+      <c r="H124" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I124" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="125">
@@ -4038,15 +4786,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>2012</v>
       </c>
       <c r="F125" t="n">
-        <v>1</v>
-      </c>
-      <c r="G125" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" t="inlineStr">
         <is>
           <t>Paysandu SC</t>
         </is>
+      </c>
+      <c r="I125" t="n">
+        <v>1997</v>
       </c>
     </row>
     <row r="126">
@@ -4067,15 +4821,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1</v>
+        <v>35285</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
-      </c>
-      <c r="G126" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I126" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="127">
@@ -4096,15 +4856,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2</v>
+        <v>7314</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
+      </c>
+      <c r="I127" t="n">
+        <v>6982</v>
       </c>
     </row>
     <row r="128">
@@ -4125,15 +4891,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2</v>
+        <v>1982</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="inlineStr">
         <is>
           <t>Cuiabá</t>
         </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49202</v>
       </c>
     </row>
     <row r="129">
@@ -4154,15 +4926,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2</v>
+        <v>336664</v>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
-      </c>
-      <c r="G129" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" t="inlineStr">
         <is>
           <t>Vila Nova FC</t>
         </is>
+      </c>
+      <c r="I129" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="130">
@@ -4183,15 +4961,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2</v>
+        <v>39634</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="inlineStr">
         <is>
           <t>Grêmio Novorizontino</t>
         </is>
+      </c>
+      <c r="I130" t="n">
+        <v>135514</v>
       </c>
     </row>
     <row r="131">
@@ -4212,15 +4996,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1</v>
+        <v>1960</v>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
-      </c>
-      <c r="G131" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2</v>
+      </c>
+      <c r="H131" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I131" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="132">
@@ -4241,15 +5031,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1</v>
+        <v>22032</v>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
-      </c>
-      <c r="G132" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2</v>
+      </c>
+      <c r="H132" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
+      </c>
+      <c r="I132" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="133">
@@ -4270,15 +5066,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1</v>
+        <v>1984</v>
       </c>
       <c r="F133" t="n">
-        <v>2</v>
-      </c>
-      <c r="G133" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G133" t="n">
+        <v>2</v>
+      </c>
+      <c r="H133" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
+      </c>
+      <c r="I133" t="n">
+        <v>7315</v>
       </c>
     </row>
     <row r="134">
@@ -4298,12 +5100,18 @@
           <t>Paysandu SC</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
+      <c r="E134" t="n">
+        <v>1997</v>
+      </c>
       <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I134" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="135">
@@ -4324,15 +5132,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1</v>
+        <v>2021</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
-      </c>
-      <c r="G135" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="inlineStr">
         <is>
           <t>Atlético Goianiense</t>
         </is>
+      </c>
+      <c r="I135" t="n">
+        <v>7314</v>
       </c>
     </row>
     <row r="136">
@@ -4353,15 +5167,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>1967</v>
       </c>
       <c r="F136" t="n">
-        <v>1</v>
-      </c>
-      <c r="G136" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
+      </c>
+      <c r="I136" t="n">
+        <v>1982</v>
       </c>
     </row>
     <row r="137">
@@ -4382,15 +5202,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1</v>
+        <v>342775</v>
       </c>
       <c r="F137" t="n">
-        <v>2</v>
-      </c>
-      <c r="G137" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2</v>
+      </c>
+      <c r="H137" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I137" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="138">
@@ -4411,15 +5237,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1</v>
+        <v>6982</v>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
-      </c>
-      <c r="G138" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="inlineStr">
         <is>
           <t>Operário-PR</t>
         </is>
+      </c>
+      <c r="I138" t="n">
+        <v>39634</v>
       </c>
     </row>
     <row r="139">
@@ -4440,15 +5272,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1</v>
+        <v>21845</v>
       </c>
       <c r="F139" t="n">
-        <v>2</v>
-      </c>
-      <c r="G139" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G139" t="n">
+        <v>2</v>
+      </c>
+      <c r="H139" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
+      </c>
+      <c r="I139" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="140">
@@ -4469,15 +5307,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1</v>
+        <v>135514</v>
       </c>
       <c r="F140" t="n">
         <v>1</v>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="inlineStr">
         <is>
           <t>Amazonas FC</t>
         </is>
+      </c>
+      <c r="I140" t="n">
+        <v>336664</v>
       </c>
     </row>
     <row r="141">
@@ -4498,15 +5342,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2</v>
+        <v>1997</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
-      </c>
-      <c r="G141" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I141" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="142">
@@ -4527,15 +5377,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>49202</v>
       </c>
       <c r="F142" t="n">
-        <v>1</v>
-      </c>
-      <c r="G142" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" t="inlineStr">
         <is>
           <t>Botafogo-SP</t>
         </is>
+      </c>
+      <c r="I142" t="n">
+        <v>1979</v>
       </c>
     </row>
     <row r="143">
@@ -4556,15 +5412,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2</v>
+        <v>7314</v>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
-      </c>
-      <c r="G143" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I143" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="144">
@@ -4585,15 +5447,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2</v>
+        <v>1982</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
-      </c>
-      <c r="G144" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
+      </c>
+      <c r="I144" t="n">
+        <v>6982</v>
       </c>
     </row>
     <row r="145">
@@ -4614,15 +5482,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>2012</v>
       </c>
       <c r="F145" t="n">
         <v>0</v>
       </c>
-      <c r="G145" t="inlineStr">
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="inlineStr">
         <is>
           <t>Cuiabá</t>
         </is>
+      </c>
+      <c r="I145" t="n">
+        <v>49202</v>
       </c>
     </row>
     <row r="146">
@@ -4643,15 +5517,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>7315</v>
       </c>
       <c r="F146" t="n">
         <v>0</v>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="inlineStr">
         <is>
           <t>Paysandu SC</t>
         </is>
+      </c>
+      <c r="I146" t="n">
+        <v>1997</v>
       </c>
     </row>
     <row r="147">
@@ -4672,15 +5552,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>336664</v>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I147" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="148">
@@ -4701,15 +5587,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1</v>
+        <v>35285</v>
       </c>
       <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="n">
         <v>3</v>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="H148" t="inlineStr">
         <is>
           <t>Vila Nova FC</t>
         </is>
+      </c>
+      <c r="I148" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="149">
@@ -4730,15 +5622,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>1979</v>
       </c>
       <c r="F149" t="n">
         <v>0</v>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="inlineStr">
         <is>
           <t>Grêmio Novorizontino</t>
         </is>
+      </c>
+      <c r="I149" t="n">
+        <v>135514</v>
       </c>
     </row>
     <row r="150">
@@ -4759,15 +5657,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1</v>
+        <v>39634</v>
       </c>
       <c r="F150" t="n">
-        <v>2</v>
-      </c>
-      <c r="G150" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G150" t="n">
+        <v>2</v>
+      </c>
+      <c r="H150" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
+      </c>
+      <c r="I150" t="n">
+        <v>21845</v>
       </c>
     </row>
     <row r="151">
@@ -4788,15 +5692,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0</v>
+        <v>1973</v>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
-      </c>
-      <c r="G151" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I151" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="152">
@@ -4817,15 +5727,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1</v>
+        <v>1960</v>
       </c>
       <c r="F152" t="n">
         <v>1</v>
       </c>
-      <c r="G152" t="inlineStr">
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I152" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="153">
@@ -4846,15 +5762,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>22032</v>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
-      </c>
-      <c r="G153" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
+      </c>
+      <c r="I153" t="n">
+        <v>1982</v>
       </c>
     </row>
     <row r="154">
@@ -4875,15 +5797,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
+        <v>2021</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
       </c>
-      <c r="G154" t="inlineStr">
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="inlineStr">
         <is>
           <t>Operário-PR</t>
         </is>
+      </c>
+      <c r="I154" t="n">
+        <v>39634</v>
       </c>
     </row>
     <row r="155">
@@ -4904,15 +5832,21 @@
         </is>
       </c>
       <c r="E155" t="n">
+        <v>135514</v>
+      </c>
+      <c r="F155" t="n">
         <v>3</v>
       </c>
-      <c r="F155" t="n">
-        <v>1</v>
-      </c>
-      <c r="G155" t="inlineStr">
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
+      </c>
+      <c r="I155" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="156">
@@ -4933,15 +5867,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2</v>
+        <v>1997</v>
       </c>
       <c r="F156" t="n">
         <v>2</v>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="G156" t="n">
+        <v>2</v>
+      </c>
+      <c r="H156" t="inlineStr">
         <is>
           <t>Atlético Goianiense</t>
         </is>
+      </c>
+      <c r="I156" t="n">
+        <v>7314</v>
       </c>
     </row>
     <row r="157">
@@ -4962,15 +5902,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0</v>
+        <v>1967</v>
       </c>
       <c r="F157" t="n">
-        <v>1</v>
-      </c>
-      <c r="G157" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
+      </c>
+      <c r="I157" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="158">
@@ -4991,15 +5937,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2</v>
+        <v>1984</v>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
-      </c>
-      <c r="G158" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G158" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I158" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="159">
@@ -5020,15 +5972,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1</v>
+        <v>21845</v>
       </c>
       <c r="F159" t="n">
         <v>1</v>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="G159" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I159" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="160">
@@ -5049,15 +6007,21 @@
         </is>
       </c>
       <c r="E160" t="n">
+        <v>342775</v>
+      </c>
+      <c r="F160" t="n">
         <v>4</v>
       </c>
-      <c r="F160" t="n">
-        <v>0</v>
-      </c>
-      <c r="G160" t="inlineStr">
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
+      </c>
+      <c r="I160" t="n">
+        <v>7315</v>
       </c>
     </row>
     <row r="161">
@@ -5078,15 +6042,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>1979</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
       </c>
-      <c r="G161" t="inlineStr">
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
+      </c>
+      <c r="I161" t="n">
+        <v>6982</v>
       </c>
     </row>
     <row r="162">
@@ -5107,15 +6077,21 @@
         </is>
       </c>
       <c r="E162" t="n">
+        <v>49202</v>
+      </c>
+      <c r="F162" t="n">
         <v>3</v>
       </c>
-      <c r="F162" t="n">
-        <v>1</v>
-      </c>
-      <c r="G162" t="inlineStr">
+      <c r="G162" t="n">
+        <v>1</v>
+      </c>
+      <c r="H162" t="inlineStr">
         <is>
           <t>Amazonas FC</t>
         </is>
+      </c>
+      <c r="I162" t="n">
+        <v>336664</v>
       </c>
     </row>
     <row r="163">
@@ -5136,15 +6112,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1</v>
+        <v>39634</v>
       </c>
       <c r="F163" t="n">
         <v>1</v>
       </c>
-      <c r="G163" t="inlineStr">
+      <c r="G163" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I163" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="164">
@@ -5165,15 +6147,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1</v>
+        <v>2012</v>
       </c>
       <c r="F164" t="n">
         <v>1</v>
       </c>
-      <c r="G164" t="inlineStr">
+      <c r="G164" t="n">
+        <v>1</v>
+      </c>
+      <c r="H164" t="inlineStr">
         <is>
           <t>Grêmio Novorizontino</t>
         </is>
+      </c>
+      <c r="I164" t="n">
+        <v>135514</v>
       </c>
     </row>
     <row r="165">
@@ -5194,15 +6182,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0</v>
+        <v>7314</v>
       </c>
       <c r="F165" t="n">
-        <v>1</v>
-      </c>
-      <c r="G165" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G165" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I165" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="166">
@@ -5223,15 +6217,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1</v>
+        <v>35285</v>
       </c>
       <c r="F166" t="n">
-        <v>2</v>
-      </c>
-      <c r="G166" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G166" t="n">
+        <v>2</v>
+      </c>
+      <c r="H166" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I166" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="167">
@@ -5252,15 +6252,21 @@
         </is>
       </c>
       <c r="E167" t="n">
+        <v>1960</v>
+      </c>
+      <c r="F167" t="n">
         <v>3</v>
       </c>
-      <c r="F167" t="n">
-        <v>1</v>
-      </c>
-      <c r="G167" t="inlineStr">
+      <c r="G167" t="n">
+        <v>1</v>
+      </c>
+      <c r="H167" t="inlineStr">
         <is>
           <t>Cuiabá</t>
         </is>
+      </c>
+      <c r="I167" t="n">
+        <v>49202</v>
       </c>
     </row>
     <row r="168">
@@ -5281,15 +6287,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1</v>
+        <v>7315</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
       </c>
-      <c r="G168" t="inlineStr">
+      <c r="G168" t="n">
+        <v>1</v>
+      </c>
+      <c r="H168" t="inlineStr">
         <is>
           <t>Vila Nova FC</t>
         </is>
+      </c>
+      <c r="I168" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="169">
@@ -5310,15 +6322,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2</v>
+        <v>1982</v>
       </c>
       <c r="F169" t="n">
+        <v>2</v>
+      </c>
+      <c r="G169" t="n">
         <v>5</v>
       </c>
-      <c r="G169" t="inlineStr">
+      <c r="H169" t="inlineStr">
         <is>
           <t>Paysandu SC</t>
         </is>
+      </c>
+      <c r="I169" t="n">
+        <v>1997</v>
       </c>
     </row>
     <row r="170">
@@ -5339,15 +6357,21 @@
         </is>
       </c>
       <c r="E170" t="n">
+        <v>6982</v>
+      </c>
+      <c r="F170" t="n">
         <v>3</v>
       </c>
-      <c r="F170" t="n">
-        <v>2</v>
-      </c>
-      <c r="G170" t="inlineStr">
+      <c r="G170" t="n">
+        <v>2</v>
+      </c>
+      <c r="H170" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I170" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="171">
@@ -5368,15 +6392,21 @@
         </is>
       </c>
       <c r="E171" t="n">
+        <v>336664</v>
+      </c>
+      <c r="F171" t="n">
         <v>3</v>
       </c>
-      <c r="F171" t="n">
-        <v>0</v>
-      </c>
-      <c r="G171" t="inlineStr">
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="inlineStr">
         <is>
           <t>Botafogo-SP</t>
         </is>
+      </c>
+      <c r="I171" t="n">
+        <v>1979</v>
       </c>
     </row>
     <row r="172">
@@ -5397,15 +6427,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0</v>
+        <v>1973</v>
       </c>
       <c r="F172" t="n">
-        <v>1</v>
-      </c>
-      <c r="G172" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
+      </c>
+      <c r="I172" t="n">
+        <v>21845</v>
       </c>
     </row>
     <row r="173">
@@ -5425,12 +6461,18 @@
           <t>Botafogo-SP</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr"/>
+      <c r="E173" t="n">
+        <v>1979</v>
+      </c>
       <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr">
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I173" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="174">
@@ -5451,15 +6493,21 @@
         </is>
       </c>
       <c r="E174" t="n">
+        <v>39634</v>
+      </c>
+      <c r="F174" t="n">
         <v>3</v>
       </c>
-      <c r="F174" t="n">
-        <v>0</v>
-      </c>
-      <c r="G174" t="inlineStr">
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="inlineStr">
         <is>
           <t>Atlético Goianiense</t>
         </is>
+      </c>
+      <c r="I174" t="n">
+        <v>7314</v>
       </c>
     </row>
     <row r="175">
@@ -5480,15 +6528,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1</v>
+        <v>1967</v>
       </c>
       <c r="F175" t="n">
         <v>1</v>
       </c>
-      <c r="G175" t="inlineStr">
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I175" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="176">
@@ -5509,15 +6563,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1</v>
+        <v>342775</v>
       </c>
       <c r="F176" t="n">
         <v>1</v>
       </c>
-      <c r="G176" t="inlineStr">
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
+      </c>
+      <c r="I176" t="n">
+        <v>1982</v>
       </c>
     </row>
     <row r="177">
@@ -5538,15 +6598,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>2</v>
+        <v>2021</v>
       </c>
       <c r="F177" t="n">
-        <v>0</v>
-      </c>
-      <c r="G177" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I177" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="178">
@@ -5567,15 +6633,21 @@
         </is>
       </c>
       <c r="E178" t="n">
+        <v>21845</v>
+      </c>
+      <c r="F178" t="n">
         <v>4</v>
       </c>
-      <c r="F178" t="n">
-        <v>2</v>
-      </c>
-      <c r="G178" t="inlineStr">
+      <c r="G178" t="n">
+        <v>2</v>
+      </c>
+      <c r="H178" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
+      </c>
+      <c r="I178" t="n">
+        <v>6982</v>
       </c>
     </row>
     <row r="179">
@@ -5596,15 +6668,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1</v>
+        <v>135514</v>
       </c>
       <c r="F179" t="n">
-        <v>0</v>
-      </c>
-      <c r="G179" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
+      </c>
+      <c r="I179" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="180">
@@ -5625,15 +6703,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1</v>
+        <v>336664</v>
       </c>
       <c r="F180" t="n">
         <v>1</v>
       </c>
-      <c r="G180" t="inlineStr">
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="inlineStr">
         <is>
           <t>Paysandu SC</t>
         </is>
+      </c>
+      <c r="I180" t="n">
+        <v>1997</v>
       </c>
     </row>
     <row r="181">
@@ -5654,15 +6738,21 @@
         </is>
       </c>
       <c r="E181" t="n">
+        <v>49202</v>
+      </c>
+      <c r="F181" t="n">
         <v>3</v>
       </c>
-      <c r="F181" t="n">
-        <v>1</v>
-      </c>
-      <c r="G181" t="inlineStr">
+      <c r="G181" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
+      </c>
+      <c r="I181" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="182">
@@ -5683,15 +6773,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>0</v>
+        <v>1979</v>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
-      </c>
-      <c r="G182" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G182" t="n">
+        <v>2</v>
+      </c>
+      <c r="H182" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I182" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="183">
@@ -5712,15 +6808,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2</v>
+        <v>2012</v>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
-      </c>
-      <c r="G183" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G183" t="n">
+        <v>1</v>
+      </c>
+      <c r="H183" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
+      </c>
+      <c r="I183" t="n">
+        <v>7315</v>
       </c>
     </row>
     <row r="184">
@@ -5740,12 +6842,18 @@
           <t>Paysandu SC</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
+      <c r="E184" t="n">
+        <v>1997</v>
+      </c>
       <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr">
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I184" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="185">
@@ -5766,15 +6874,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>0</v>
+        <v>35285</v>
       </c>
       <c r="F185" t="n">
         <v>0</v>
       </c>
-      <c r="G185" t="inlineStr">
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="inlineStr">
         <is>
           <t>Operário-PR</t>
         </is>
+      </c>
+      <c r="I185" t="n">
+        <v>39634</v>
       </c>
     </row>
     <row r="186">
@@ -5795,15 +6909,21 @@
         </is>
       </c>
       <c r="E186" t="n">
+        <v>22032</v>
+      </c>
+      <c r="F186" t="n">
         <v>4</v>
       </c>
-      <c r="F186" t="n">
-        <v>0</v>
-      </c>
-      <c r="G186" t="inlineStr">
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="inlineStr">
         <is>
           <t>Grêmio Novorizontino</t>
         </is>
+      </c>
+      <c r="I186" t="n">
+        <v>135514</v>
       </c>
     </row>
     <row r="187">
@@ -5823,12 +6943,18 @@
           <t>Goiás</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr"/>
+      <c r="E187" t="n">
+        <v>1960</v>
+      </c>
       <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr">
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I187" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="188">
@@ -5849,15 +6975,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1</v>
+        <v>1982</v>
       </c>
       <c r="F188" t="n">
         <v>1</v>
       </c>
-      <c r="G188" t="inlineStr">
+      <c r="G188" t="n">
+        <v>1</v>
+      </c>
+      <c r="H188" t="inlineStr">
         <is>
           <t>Amazonas FC</t>
         </is>
+      </c>
+      <c r="I188" t="n">
+        <v>336664</v>
       </c>
     </row>
     <row r="189">
@@ -5878,15 +7010,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2</v>
+        <v>6982</v>
       </c>
       <c r="F189" t="n">
-        <v>1</v>
-      </c>
-      <c r="G189" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G189" t="n">
+        <v>1</v>
+      </c>
+      <c r="H189" t="inlineStr">
         <is>
           <t>Vila Nova FC</t>
         </is>
+      </c>
+      <c r="I189" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="190">
@@ -5907,15 +7045,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2</v>
+        <v>1973</v>
       </c>
       <c r="F190" t="n">
         <v>2</v>
       </c>
-      <c r="G190" t="inlineStr">
+      <c r="G190" t="n">
+        <v>2</v>
+      </c>
+      <c r="H190" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I190" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="191">
@@ -5936,15 +7080,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>0</v>
+        <v>7314</v>
       </c>
       <c r="F191" t="n">
         <v>0</v>
       </c>
-      <c r="G191" t="inlineStr">
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
+      </c>
+      <c r="I191" t="n">
+        <v>21845</v>
       </c>
     </row>
     <row r="192">
@@ -5965,15 +7115,21 @@
         </is>
       </c>
       <c r="E192" t="n">
+        <v>7315</v>
+      </c>
+      <c r="F192" t="n">
         <v>5</v>
       </c>
-      <c r="F192" t="n">
-        <v>0</v>
-      </c>
-      <c r="G192" t="inlineStr">
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="inlineStr">
         <is>
           <t>Botafogo-SP</t>
         </is>
+      </c>
+      <c r="I192" t="n">
+        <v>1979</v>
       </c>
     </row>
     <row r="193">
@@ -5994,15 +7150,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1</v>
+        <v>1997</v>
       </c>
       <c r="F193" t="n">
         <v>1</v>
       </c>
-      <c r="G193" t="inlineStr">
+      <c r="G193" t="n">
+        <v>1</v>
+      </c>
+      <c r="H193" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I193" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="194">
@@ -6023,15 +7185,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1</v>
+        <v>1984</v>
       </c>
       <c r="F194" t="n">
-        <v>0</v>
-      </c>
-      <c r="G194" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="inlineStr">
         <is>
           <t>Cuiabá</t>
         </is>
+      </c>
+      <c r="I194" t="n">
+        <v>49202</v>
       </c>
     </row>
     <row r="195">
@@ -6052,15 +7220,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1</v>
+        <v>1960</v>
       </c>
       <c r="F195" t="n">
         <v>1</v>
       </c>
-      <c r="G195" t="inlineStr">
+      <c r="G195" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I195" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="196">
@@ -6081,15 +7255,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>2021</v>
       </c>
       <c r="F196" t="n">
-        <v>2</v>
-      </c>
-      <c r="G196" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G196" t="n">
+        <v>2</v>
+      </c>
+      <c r="H196" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
+      </c>
+      <c r="I196" t="n">
+        <v>1982</v>
       </c>
     </row>
     <row r="197">
@@ -6110,15 +7290,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>0</v>
+        <v>2012</v>
       </c>
       <c r="F197" t="n">
-        <v>2</v>
-      </c>
-      <c r="G197" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G197" t="n">
+        <v>2</v>
+      </c>
+      <c r="H197" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I197" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="198">
@@ -6139,15 +7325,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1</v>
+        <v>39634</v>
       </c>
       <c r="F198" t="n">
-        <v>0</v>
-      </c>
-      <c r="G198" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I198" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="199">
@@ -6168,15 +7360,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>2</v>
+        <v>1979</v>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
-      </c>
-      <c r="G199" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1</v>
+      </c>
+      <c r="H199" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
+      </c>
+      <c r="I199" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="200">
@@ -6197,15 +7395,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>2</v>
+        <v>336664</v>
       </c>
       <c r="F200" t="n">
         <v>2</v>
       </c>
-      <c r="G200" t="inlineStr">
+      <c r="G200" t="n">
+        <v>2</v>
+      </c>
+      <c r="H200" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
+      </c>
+      <c r="I200" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="201">
@@ -6226,15 +7430,21 @@
         </is>
       </c>
       <c r="E201" t="n">
+        <v>21845</v>
+      </c>
+      <c r="F201" t="n">
         <v>3</v>
       </c>
-      <c r="F201" t="n">
-        <v>2</v>
-      </c>
-      <c r="G201" t="inlineStr">
+      <c r="G201" t="n">
+        <v>2</v>
+      </c>
+      <c r="H201" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I201" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="202">
@@ -6255,15 +7465,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1</v>
+        <v>135514</v>
       </c>
       <c r="F202" t="n">
         <v>1</v>
       </c>
-      <c r="G202" t="inlineStr">
+      <c r="G202" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
+      </c>
+      <c r="I202" t="n">
+        <v>7315</v>
       </c>
     </row>
     <row r="203">
@@ -6284,15 +7500,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1</v>
+        <v>1967</v>
       </c>
       <c r="F203" t="n">
         <v>1</v>
       </c>
-      <c r="G203" t="inlineStr">
+      <c r="G203" t="n">
+        <v>1</v>
+      </c>
+      <c r="H203" t="inlineStr">
         <is>
           <t>Paysandu SC</t>
         </is>
+      </c>
+      <c r="I203" t="n">
+        <v>1997</v>
       </c>
     </row>
     <row r="204">
@@ -6313,15 +7535,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1</v>
+        <v>342775</v>
       </c>
       <c r="F204" t="n">
         <v>1</v>
       </c>
-      <c r="G204" t="inlineStr">
+      <c r="G204" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" t="inlineStr">
         <is>
           <t>Atlético Goianiense</t>
         </is>
+      </c>
+      <c r="I204" t="n">
+        <v>7314</v>
       </c>
     </row>
     <row r="205">
@@ -6342,15 +7570,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>2</v>
+        <v>49202</v>
       </c>
       <c r="F205" t="n">
-        <v>0</v>
-      </c>
-      <c r="G205" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
+      </c>
+      <c r="I205" t="n">
+        <v>6982</v>
       </c>
     </row>
     <row r="206">
@@ -6371,15 +7605,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>2</v>
+        <v>35285</v>
       </c>
       <c r="F206" t="n">
-        <v>1</v>
-      </c>
-      <c r="G206" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G206" t="n">
+        <v>1</v>
+      </c>
+      <c r="H206" t="inlineStr">
         <is>
           <t>Amazonas FC</t>
         </is>
+      </c>
+      <c r="I206" t="n">
+        <v>336664</v>
       </c>
     </row>
     <row r="207">
@@ -6400,15 +7640,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>0</v>
+        <v>1982</v>
       </c>
       <c r="F207" t="n">
         <v>0</v>
       </c>
-      <c r="G207" t="inlineStr">
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
+      </c>
+      <c r="I207" t="n">
+        <v>21845</v>
       </c>
     </row>
     <row r="208">
@@ -6428,12 +7674,18 @@
           <t>Criciúma</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
+      <c r="E208" t="n">
+        <v>1984</v>
+      </c>
       <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr">
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I208" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="209">
@@ -6454,15 +7706,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>0</v>
+        <v>1973</v>
       </c>
       <c r="F209" t="n">
-        <v>1</v>
-      </c>
-      <c r="G209" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G209" t="n">
+        <v>1</v>
+      </c>
+      <c r="H209" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I209" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="210">
@@ -6483,15 +7741,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>2</v>
+        <v>1960</v>
       </c>
       <c r="F210" t="n">
-        <v>1</v>
-      </c>
-      <c r="G210" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G210" t="n">
+        <v>1</v>
+      </c>
+      <c r="H210" t="inlineStr">
         <is>
           <t>Operário-PR</t>
         </is>
+      </c>
+      <c r="I210" t="n">
+        <v>39634</v>
       </c>
     </row>
     <row r="211">
@@ -6512,15 +7776,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>0</v>
+        <v>6982</v>
       </c>
       <c r="F211" t="n">
         <v>0</v>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="inlineStr">
         <is>
           <t>Grêmio Novorizontino</t>
         </is>
+      </c>
+      <c r="I211" t="n">
+        <v>135514</v>
       </c>
     </row>
     <row r="212">
@@ -6541,15 +7811,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>2</v>
+        <v>7315</v>
       </c>
       <c r="F212" t="n">
-        <v>0</v>
-      </c>
-      <c r="G212" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="inlineStr">
         <is>
           <t>Cuiabá</t>
         </is>
+      </c>
+      <c r="I212" t="n">
+        <v>49202</v>
       </c>
     </row>
     <row r="213">
@@ -6570,15 +7846,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>2</v>
+        <v>7314</v>
       </c>
       <c r="F213" t="n">
-        <v>0</v>
-      </c>
-      <c r="G213" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="inlineStr">
         <is>
           <t>Botafogo-SP</t>
         </is>
+      </c>
+      <c r="I213" t="n">
+        <v>1979</v>
       </c>
     </row>
     <row r="214">
@@ -6599,15 +7881,21 @@
         </is>
       </c>
       <c r="E214" t="n">
+        <v>1984</v>
+      </c>
+      <c r="F214" t="n">
         <v>4</v>
       </c>
-      <c r="F214" t="n">
-        <v>2</v>
-      </c>
-      <c r="G214" t="inlineStr">
+      <c r="G214" t="n">
+        <v>2</v>
+      </c>
+      <c r="H214" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I214" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="215">
@@ -6628,15 +7916,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>0</v>
+        <v>1997</v>
       </c>
       <c r="F215" t="n">
-        <v>1</v>
-      </c>
-      <c r="G215" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G215" t="n">
+        <v>1</v>
+      </c>
+      <c r="H215" t="inlineStr">
         <is>
           <t>Vila Nova FC</t>
         </is>
+      </c>
+      <c r="I215" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="216">
@@ -6657,15 +7951,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1</v>
+        <v>22032</v>
       </c>
       <c r="F216" t="n">
-        <v>0</v>
-      </c>
-      <c r="G216" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I216" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="217">
@@ -6686,15 +7986,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1</v>
+        <v>135514</v>
       </c>
       <c r="F217" t="n">
-        <v>2</v>
-      </c>
-      <c r="G217" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G217" t="n">
+        <v>2</v>
+      </c>
+      <c r="H217" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
+      </c>
+      <c r="I217" t="n">
+        <v>1982</v>
       </c>
     </row>
     <row r="218">
@@ -6714,12 +8020,18 @@
           <t>Volta Redonda</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr"/>
+      <c r="E218" t="n">
+        <v>6982</v>
+      </c>
       <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr">
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I218" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="219">
@@ -6740,15 +8052,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>2</v>
+        <v>336664</v>
       </c>
       <c r="F219" t="n">
         <v>2</v>
       </c>
-      <c r="G219" t="inlineStr">
+      <c r="G219" t="n">
+        <v>2</v>
+      </c>
+      <c r="H219" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
+      </c>
+      <c r="I219" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="220">
@@ -6769,15 +8087,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1</v>
+        <v>2012</v>
       </c>
       <c r="F220" t="n">
         <v>1</v>
       </c>
-      <c r="G220" t="inlineStr">
+      <c r="G220" t="n">
+        <v>1</v>
+      </c>
+      <c r="H220" t="inlineStr">
         <is>
           <t>Botafogo-SP</t>
         </is>
+      </c>
+      <c r="I220" t="n">
+        <v>1979</v>
       </c>
     </row>
     <row r="221">
@@ -6798,15 +8122,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>2</v>
+        <v>2021</v>
       </c>
       <c r="F221" t="n">
-        <v>0</v>
-      </c>
-      <c r="G221" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
+      </c>
+      <c r="I221" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="222">
@@ -6827,15 +8157,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1</v>
+        <v>1967</v>
       </c>
       <c r="F222" t="n">
         <v>1</v>
       </c>
-      <c r="G222" t="inlineStr">
+      <c r="G222" t="n">
+        <v>1</v>
+      </c>
+      <c r="H222" t="inlineStr">
         <is>
           <t>Cuiabá</t>
         </is>
+      </c>
+      <c r="I222" t="n">
+        <v>49202</v>
       </c>
     </row>
     <row r="223">
@@ -6856,15 +8192,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>2</v>
+        <v>21845</v>
       </c>
       <c r="F223" t="n">
-        <v>0</v>
-      </c>
-      <c r="G223" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="inlineStr">
         <is>
           <t>Paysandu SC</t>
         </is>
+      </c>
+      <c r="I223" t="n">
+        <v>1997</v>
       </c>
     </row>
     <row r="224">
@@ -6885,15 +8227,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1</v>
+        <v>7314</v>
       </c>
       <c r="F224" t="n">
+        <v>1</v>
+      </c>
+      <c r="G224" t="n">
         <v>3</v>
       </c>
-      <c r="G224" t="inlineStr">
+      <c r="H224" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I224" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="225">
@@ -6914,15 +8262,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>0</v>
+        <v>6982</v>
       </c>
       <c r="F225" t="n">
-        <v>1</v>
-      </c>
-      <c r="G225" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G225" t="n">
+        <v>1</v>
+      </c>
+      <c r="H225" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I225" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="226">
@@ -6943,15 +8297,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1</v>
+        <v>342775</v>
       </c>
       <c r="F226" t="n">
         <v>1</v>
       </c>
-      <c r="G226" t="inlineStr">
+      <c r="G226" t="n">
+        <v>1</v>
+      </c>
+      <c r="H226" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I226" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="227">
@@ -6972,15 +8332,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>0</v>
+        <v>39634</v>
       </c>
       <c r="F227" t="n">
         <v>0</v>
       </c>
-      <c r="G227" t="inlineStr">
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
+      </c>
+      <c r="I227" t="n">
+        <v>7315</v>
       </c>
     </row>
     <row r="228">
@@ -7001,15 +8367,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>0</v>
+        <v>342775</v>
       </c>
       <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="n">
         <v>4</v>
       </c>
-      <c r="G228" t="inlineStr">
+      <c r="H228" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
+      </c>
+      <c r="I228" t="n">
+        <v>21845</v>
       </c>
     </row>
     <row r="229">
@@ -7030,15 +8402,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>2</v>
+        <v>1984</v>
       </c>
       <c r="F229" t="n">
-        <v>0</v>
-      </c>
-      <c r="G229" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="inlineStr">
         <is>
           <t>Grêmio Novorizontino</t>
         </is>
+      </c>
+      <c r="I229" t="n">
+        <v>135514</v>
       </c>
     </row>
     <row r="230">
@@ -7059,15 +8437,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>0</v>
+        <v>1982</v>
       </c>
       <c r="F230" t="n">
         <v>0</v>
       </c>
-      <c r="G230" t="inlineStr">
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I230" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="231">
@@ -7088,15 +8472,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>1</v>
+        <v>1960</v>
       </c>
       <c r="F231" t="n">
-        <v>0</v>
-      </c>
-      <c r="G231" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
+      </c>
+      <c r="I231" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="232">
@@ -7117,15 +8507,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>0</v>
+        <v>22032</v>
       </c>
       <c r="F232" t="n">
-        <v>1</v>
-      </c>
-      <c r="G232" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G232" t="n">
+        <v>1</v>
+      </c>
+      <c r="H232" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I232" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="233">
@@ -7146,15 +8542,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>1</v>
+        <v>1997</v>
       </c>
       <c r="F233" t="n">
-        <v>2</v>
-      </c>
-      <c r="G233" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G233" t="n">
+        <v>2</v>
+      </c>
+      <c r="H233" t="inlineStr">
         <is>
           <t>Operário-PR</t>
         </is>
+      </c>
+      <c r="I233" t="n">
+        <v>39634</v>
       </c>
     </row>
     <row r="234">
@@ -7175,15 +8577,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>0</v>
+        <v>35285</v>
       </c>
       <c r="F234" t="n">
         <v>0</v>
       </c>
-      <c r="G234" t="inlineStr">
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
+      </c>
+      <c r="I234" t="n">
+        <v>6982</v>
       </c>
     </row>
     <row r="235">
@@ -7204,15 +8612,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>2</v>
+        <v>49202</v>
       </c>
       <c r="F235" t="n">
         <v>2</v>
       </c>
-      <c r="G235" t="inlineStr">
+      <c r="G235" t="n">
+        <v>2</v>
+      </c>
+      <c r="H235" t="inlineStr">
         <is>
           <t>Atlético Goianiense</t>
         </is>
+      </c>
+      <c r="I235" t="n">
+        <v>7314</v>
       </c>
     </row>
     <row r="236">
@@ -7233,15 +8647,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>2</v>
+        <v>1979</v>
       </c>
       <c r="F236" t="n">
-        <v>0</v>
-      </c>
-      <c r="G236" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="inlineStr">
         <is>
           <t>Vila Nova FC</t>
         </is>
+      </c>
+      <c r="I236" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="237">
@@ -7262,15 +8682,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>1</v>
+        <v>7315</v>
       </c>
       <c r="F237" t="n">
-        <v>2</v>
-      </c>
-      <c r="G237" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G237" t="n">
+        <v>2</v>
+      </c>
+      <c r="H237" t="inlineStr">
         <is>
           <t>Amazonas FC</t>
         </is>
+      </c>
+      <c r="I237" t="n">
+        <v>336664</v>
       </c>
     </row>
     <row r="238">
@@ -7291,15 +8717,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>0</v>
+        <v>2012</v>
       </c>
       <c r="F238" t="n">
-        <v>1</v>
-      </c>
-      <c r="G238" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G238" t="n">
+        <v>1</v>
+      </c>
+      <c r="H238" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I238" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="239">
@@ -7320,15 +8752,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1</v>
+        <v>39634</v>
       </c>
       <c r="F239" t="n">
-        <v>0</v>
-      </c>
-      <c r="G239" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
+      </c>
+      <c r="I239" t="n">
+        <v>1982</v>
       </c>
     </row>
     <row r="240">
@@ -7349,15 +8787,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>2</v>
+        <v>22032</v>
       </c>
       <c r="F240" t="n">
-        <v>0</v>
-      </c>
-      <c r="G240" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="inlineStr">
         <is>
           <t>Paysandu SC</t>
         </is>
+      </c>
+      <c r="I240" t="n">
+        <v>1997</v>
       </c>
     </row>
     <row r="241">
@@ -7378,15 +8822,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>2</v>
+        <v>1960</v>
       </c>
       <c r="F241" t="n">
+        <v>2</v>
+      </c>
+      <c r="G241" t="n">
         <v>3</v>
       </c>
-      <c r="G241" t="inlineStr">
+      <c r="H241" t="inlineStr">
         <is>
           <t>Botafogo-SP</t>
         </is>
+      </c>
+      <c r="I241" t="n">
+        <v>1979</v>
       </c>
     </row>
     <row r="242">
@@ -7407,15 +8857,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>2</v>
+        <v>1967</v>
       </c>
       <c r="F242" t="n">
-        <v>1</v>
-      </c>
-      <c r="G242" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G242" t="n">
+        <v>1</v>
+      </c>
+      <c r="H242" t="inlineStr">
         <is>
           <t>Grêmio Novorizontino</t>
         </is>
+      </c>
+      <c r="I242" t="n">
+        <v>135514</v>
       </c>
     </row>
     <row r="243">
@@ -7436,15 +8892,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>2</v>
+        <v>7314</v>
       </c>
       <c r="F243" t="n">
-        <v>0</v>
-      </c>
-      <c r="G243" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="inlineStr">
         <is>
           <t>Amazonas FC</t>
         </is>
+      </c>
+      <c r="I243" t="n">
+        <v>336664</v>
       </c>
     </row>
     <row r="244">
@@ -7465,15 +8927,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>0</v>
+        <v>6982</v>
       </c>
       <c r="F244" t="n">
-        <v>2</v>
-      </c>
-      <c r="G244" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G244" t="n">
+        <v>2</v>
+      </c>
+      <c r="H244" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I244" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="245">
@@ -7494,15 +8962,21 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>2</v>
+        <v>21845</v>
       </c>
       <c r="F245" t="n">
         <v>2</v>
       </c>
-      <c r="G245" t="inlineStr">
+      <c r="G245" t="n">
+        <v>2</v>
+      </c>
+      <c r="H245" t="inlineStr">
         <is>
           <t>Vila Nova FC</t>
         </is>
+      </c>
+      <c r="I245" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="246">
@@ -7523,15 +8997,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>2</v>
+        <v>35285</v>
       </c>
       <c r="F246" t="n">
         <v>2</v>
       </c>
-      <c r="G246" t="inlineStr">
+      <c r="G246" t="n">
+        <v>2</v>
+      </c>
+      <c r="H246" t="inlineStr">
         <is>
           <t>Cuiabá</t>
         </is>
+      </c>
+      <c r="I246" t="n">
+        <v>49202</v>
       </c>
     </row>
     <row r="247">
@@ -7552,15 +9032,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>2</v>
+        <v>1973</v>
       </c>
       <c r="F247" t="n">
-        <v>0</v>
-      </c>
-      <c r="G247" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
+      </c>
+      <c r="I247" t="n">
+        <v>7315</v>
       </c>
     </row>
     <row r="248">
@@ -7581,15 +9067,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1</v>
+        <v>336664</v>
       </c>
       <c r="F248" t="n">
+        <v>1</v>
+      </c>
+      <c r="G248" t="n">
         <v>3</v>
       </c>
-      <c r="G248" t="inlineStr">
+      <c r="H248" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I248" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="249">
@@ -7610,15 +9102,21 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1</v>
+        <v>1997</v>
       </c>
       <c r="F249" t="n">
-        <v>2</v>
-      </c>
-      <c r="G249" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G249" t="n">
+        <v>2</v>
+      </c>
+      <c r="H249" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
+      </c>
+      <c r="I249" t="n">
+        <v>6982</v>
       </c>
     </row>
     <row r="250">
@@ -7639,15 +9137,21 @@
         </is>
       </c>
       <c r="E250" t="n">
+        <v>1982</v>
+      </c>
+      <c r="F250" t="n">
         <v>4</v>
       </c>
-      <c r="F250" t="n">
-        <v>0</v>
-      </c>
-      <c r="G250" t="inlineStr">
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I250" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="251">
@@ -7668,15 +9172,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1</v>
+        <v>1979</v>
       </c>
       <c r="F251" t="n">
+        <v>1</v>
+      </c>
+      <c r="G251" t="n">
         <v>3</v>
       </c>
-      <c r="G251" t="inlineStr">
+      <c r="H251" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I251" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="252">
@@ -7697,15 +9207,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2</v>
+        <v>1984</v>
       </c>
       <c r="F252" t="n">
-        <v>0</v>
-      </c>
-      <c r="G252" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
+      </c>
+      <c r="I252" t="n">
+        <v>21845</v>
       </c>
     </row>
     <row r="253">
@@ -7726,15 +9242,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1</v>
+        <v>1973</v>
       </c>
       <c r="F253" t="n">
         <v>1</v>
       </c>
-      <c r="G253" t="inlineStr">
+      <c r="G253" t="n">
+        <v>1</v>
+      </c>
+      <c r="H253" t="inlineStr">
         <is>
           <t>Operário-PR</t>
         </is>
+      </c>
+      <c r="I253" t="n">
+        <v>39634</v>
       </c>
     </row>
     <row r="254">
@@ -7755,15 +9277,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>2</v>
+        <v>7315</v>
       </c>
       <c r="F254" t="n">
-        <v>1</v>
-      </c>
-      <c r="G254" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G254" t="n">
+        <v>1</v>
+      </c>
+      <c r="H254" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
+      </c>
+      <c r="I254" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="255">
@@ -7784,15 +9312,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>1</v>
+        <v>135514</v>
       </c>
       <c r="F255" t="n">
         <v>1</v>
       </c>
-      <c r="G255" t="inlineStr">
+      <c r="G255" t="n">
+        <v>1</v>
+      </c>
+      <c r="H255" t="inlineStr">
         <is>
           <t>Atlético Goianiense</t>
         </is>
+      </c>
+      <c r="I255" t="n">
+        <v>7314</v>
       </c>
     </row>
     <row r="256">
@@ -7813,15 +9347,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>1</v>
+        <v>49202</v>
       </c>
       <c r="F256" t="n">
-        <v>0</v>
-      </c>
-      <c r="G256" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+      <c r="H256" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I256" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="257">
@@ -7842,15 +9382,21 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>1</v>
+        <v>2021</v>
       </c>
       <c r="F257" t="n">
         <v>1</v>
       </c>
-      <c r="G257" t="inlineStr">
+      <c r="G257" t="n">
+        <v>1</v>
+      </c>
+      <c r="H257" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I257" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="258">
@@ -7871,15 +9417,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>0</v>
+        <v>6982</v>
       </c>
       <c r="F258" t="n">
         <v>0</v>
       </c>
-      <c r="G258" t="inlineStr">
+      <c r="G258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H258" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I258" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="259">
@@ -7900,15 +9452,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>0</v>
+        <v>1982</v>
       </c>
       <c r="F259" t="n">
         <v>0</v>
       </c>
-      <c r="G259" t="inlineStr">
+      <c r="G259" t="n">
+        <v>0</v>
+      </c>
+      <c r="H259" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
+      </c>
+      <c r="I259" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="260">
@@ -7929,15 +9487,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>0</v>
+        <v>1997</v>
       </c>
       <c r="F260" t="n">
         <v>0</v>
       </c>
-      <c r="G260" t="inlineStr">
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+      <c r="H260" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
+      </c>
+      <c r="I260" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="261">
@@ -7958,15 +9522,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1</v>
+        <v>2021</v>
       </c>
       <c r="F261" t="n">
         <v>1</v>
       </c>
-      <c r="G261" t="inlineStr">
+      <c r="G261" t="n">
+        <v>1</v>
+      </c>
+      <c r="H261" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I261" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="262">
@@ -7987,15 +9557,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>1</v>
+        <v>39634</v>
       </c>
       <c r="F262" t="n">
         <v>1</v>
       </c>
-      <c r="G262" t="inlineStr">
+      <c r="G262" t="n">
+        <v>1</v>
+      </c>
+      <c r="H262" t="inlineStr">
         <is>
           <t>Cuiabá</t>
         </is>
+      </c>
+      <c r="I262" t="n">
+        <v>49202</v>
       </c>
     </row>
     <row r="263">
@@ -8016,15 +9592,21 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>2</v>
+        <v>342775</v>
       </c>
       <c r="F263" t="n">
-        <v>0</v>
-      </c>
-      <c r="G263" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G263" t="n">
+        <v>0</v>
+      </c>
+      <c r="H263" t="inlineStr">
         <is>
           <t>Botafogo-SP</t>
         </is>
+      </c>
+      <c r="I263" t="n">
+        <v>1979</v>
       </c>
     </row>
     <row r="264">
@@ -8045,15 +9627,21 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>1</v>
+        <v>35285</v>
       </c>
       <c r="F264" t="n">
-        <v>2</v>
-      </c>
-      <c r="G264" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G264" t="n">
+        <v>2</v>
+      </c>
+      <c r="H264" t="inlineStr">
         <is>
           <t>Grêmio Novorizontino</t>
         </is>
+      </c>
+      <c r="I264" t="n">
+        <v>135514</v>
       </c>
     </row>
     <row r="265">
@@ -8074,15 +9662,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>2</v>
+        <v>22032</v>
       </c>
       <c r="F265" t="n">
-        <v>0</v>
-      </c>
-      <c r="G265" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" t="inlineStr">
         <is>
           <t>Amazonas FC</t>
         </is>
+      </c>
+      <c r="I265" t="n">
+        <v>336664</v>
       </c>
     </row>
     <row r="266">
@@ -8103,15 +9697,21 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>2</v>
+        <v>7314</v>
       </c>
       <c r="F266" t="n">
-        <v>1</v>
-      </c>
-      <c r="G266" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G266" t="n">
+        <v>1</v>
+      </c>
+      <c r="H266" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
+      </c>
+      <c r="I266" t="n">
+        <v>7315</v>
       </c>
     </row>
     <row r="267">
@@ -8132,15 +9732,21 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>2</v>
+        <v>21845</v>
       </c>
       <c r="F267" t="n">
+        <v>2</v>
+      </c>
+      <c r="G267" t="n">
         <v>3</v>
       </c>
-      <c r="G267" t="inlineStr">
+      <c r="H267" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I267" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="268">
@@ -8161,15 +9767,21 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>1</v>
+        <v>1979</v>
       </c>
       <c r="F268" t="n">
         <v>1</v>
       </c>
-      <c r="G268" t="inlineStr">
+      <c r="G268" t="n">
+        <v>1</v>
+      </c>
+      <c r="H268" t="inlineStr">
         <is>
           <t>Operário-PR</t>
         </is>
+      </c>
+      <c r="I268" t="n">
+        <v>39634</v>
       </c>
     </row>
     <row r="269">
@@ -8190,15 +9802,21 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>1</v>
+        <v>135514</v>
       </c>
       <c r="F269" t="n">
-        <v>0</v>
-      </c>
-      <c r="G269" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G269" t="n">
+        <v>0</v>
+      </c>
+      <c r="H269" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I269" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="270">
@@ -8219,15 +9837,21 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>1</v>
+        <v>1960</v>
       </c>
       <c r="F270" t="n">
-        <v>0</v>
-      </c>
-      <c r="G270" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G270" t="n">
+        <v>0</v>
+      </c>
+      <c r="H270" t="inlineStr">
         <is>
           <t>Paysandu SC</t>
         </is>
+      </c>
+      <c r="I270" t="n">
+        <v>1997</v>
       </c>
     </row>
     <row r="271">
@@ -8248,15 +9872,21 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>1</v>
+        <v>336664</v>
       </c>
       <c r="F271" t="n">
-        <v>0</v>
-      </c>
-      <c r="G271" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+      <c r="H271" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
+      </c>
+      <c r="I271" t="n">
+        <v>6982</v>
       </c>
     </row>
     <row r="272">
@@ -8277,15 +9907,21 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>2</v>
+        <v>7315</v>
       </c>
       <c r="F272" t="n">
         <v>2</v>
       </c>
-      <c r="G272" t="inlineStr">
+      <c r="G272" t="n">
+        <v>2</v>
+      </c>
+      <c r="H272" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I272" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="273">
@@ -8306,15 +9942,21 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>0</v>
+        <v>2012</v>
       </c>
       <c r="F273" t="n">
-        <v>1</v>
-      </c>
-      <c r="G273" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G273" t="n">
+        <v>1</v>
+      </c>
+      <c r="H273" t="inlineStr">
         <is>
           <t>Atlético Goianiense</t>
         </is>
+      </c>
+      <c r="I273" t="n">
+        <v>7314</v>
       </c>
     </row>
     <row r="274">
@@ -8335,15 +9977,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>1</v>
+        <v>1973</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
-      </c>
-      <c r="G274" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G274" t="n">
+        <v>0</v>
+      </c>
+      <c r="H274" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
+      </c>
+      <c r="I274" t="n">
+        <v>1982</v>
       </c>
     </row>
     <row r="275">
@@ -8364,15 +10012,21 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>1</v>
+        <v>1984</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
-      </c>
-      <c r="G275" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G275" t="n">
+        <v>0</v>
+      </c>
+      <c r="H275" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I275" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="276">
@@ -8393,15 +10047,21 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>2</v>
+        <v>1967</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
-      </c>
-      <c r="G276" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0</v>
+      </c>
+      <c r="H276" t="inlineStr">
         <is>
           <t>Vila Nova FC</t>
         </is>
+      </c>
+      <c r="I276" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="277">
@@ -8422,15 +10082,21 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>1</v>
+        <v>49202</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
-      </c>
-      <c r="G277" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G277" t="n">
+        <v>0</v>
+      </c>
+      <c r="H277" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
+      </c>
+      <c r="I277" t="n">
+        <v>21845</v>
       </c>
     </row>
     <row r="278">
@@ -8451,15 +10117,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>0</v>
+        <v>1997</v>
       </c>
       <c r="F278" t="n">
-        <v>1</v>
-      </c>
-      <c r="G278" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G278" t="n">
+        <v>1</v>
+      </c>
+      <c r="H278" t="inlineStr">
         <is>
           <t>Grêmio Novorizontino</t>
         </is>
+      </c>
+      <c r="I278" t="n">
+        <v>135514</v>
       </c>
     </row>
     <row r="279">
@@ -8480,15 +10152,21 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>1</v>
+        <v>35285</v>
       </c>
       <c r="F279" t="n">
         <v>1</v>
       </c>
-      <c r="G279" t="inlineStr">
+      <c r="G279" t="n">
+        <v>1</v>
+      </c>
+      <c r="H279" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
+      </c>
+      <c r="I279" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="280">
@@ -8509,15 +10187,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>0</v>
+        <v>342775</v>
       </c>
       <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="n">
         <v>3</v>
       </c>
-      <c r="G280" t="inlineStr">
+      <c r="H280" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I280" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="281">
@@ -8538,15 +10222,21 @@
         </is>
       </c>
       <c r="E281" t="n">
+        <v>22032</v>
+      </c>
+      <c r="F281" t="n">
         <v>3</v>
       </c>
-      <c r="F281" t="n">
-        <v>2</v>
-      </c>
-      <c r="G281" t="inlineStr">
+      <c r="G281" t="n">
+        <v>2</v>
+      </c>
+      <c r="H281" t="inlineStr">
         <is>
           <t>Botafogo-SP</t>
         </is>
+      </c>
+      <c r="I281" t="n">
+        <v>1979</v>
       </c>
     </row>
     <row r="282">
@@ -8567,15 +10257,21 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>2</v>
+        <v>2021</v>
       </c>
       <c r="F282" t="n">
         <v>2</v>
       </c>
-      <c r="G282" t="inlineStr">
+      <c r="G282" t="n">
+        <v>2</v>
+      </c>
+      <c r="H282" t="inlineStr">
         <is>
           <t>Cuiabá</t>
         </is>
+      </c>
+      <c r="I282" t="n">
+        <v>49202</v>
       </c>
     </row>
     <row r="283">
@@ -8596,15 +10292,21 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>2</v>
+        <v>39634</v>
       </c>
       <c r="F283" t="n">
-        <v>1</v>
-      </c>
-      <c r="G283" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G283" t="n">
+        <v>1</v>
+      </c>
+      <c r="H283" t="inlineStr">
         <is>
           <t>Amazonas FC</t>
         </is>
+      </c>
+      <c r="I283" t="n">
+        <v>336664</v>
       </c>
     </row>
     <row r="284">
@@ -8625,15 +10327,21 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>2</v>
+        <v>6982</v>
       </c>
       <c r="F284" t="n">
-        <v>1</v>
-      </c>
-      <c r="G284" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G284" t="n">
+        <v>1</v>
+      </c>
+      <c r="H284" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I284" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="285">
@@ -8654,15 +10362,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>0</v>
+        <v>1982</v>
       </c>
       <c r="F285" t="n">
-        <v>2</v>
-      </c>
-      <c r="G285" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G285" t="n">
+        <v>2</v>
+      </c>
+      <c r="H285" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I285" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="286">
@@ -8683,15 +10397,21 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>1</v>
+        <v>7314</v>
       </c>
       <c r="F286" t="n">
-        <v>0</v>
-      </c>
-      <c r="G286" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G286" t="n">
+        <v>0</v>
+      </c>
+      <c r="H286" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
+      </c>
+      <c r="I286" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="287">
@@ -8712,15 +10432,21 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>0</v>
+        <v>21845</v>
       </c>
       <c r="F287" t="n">
-        <v>1</v>
-      </c>
-      <c r="G287" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G287" t="n">
+        <v>1</v>
+      </c>
+      <c r="H287" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
+      </c>
+      <c r="I287" t="n">
+        <v>7315</v>
       </c>
     </row>
     <row r="288">
@@ -8741,15 +10467,21 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>1</v>
+        <v>1967</v>
       </c>
       <c r="F288" t="n">
-        <v>0</v>
-      </c>
-      <c r="G288" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G288" t="n">
+        <v>0</v>
+      </c>
+      <c r="H288" t="inlineStr">
         <is>
           <t>Operário-PR</t>
         </is>
+      </c>
+      <c r="I288" t="n">
+        <v>39634</v>
       </c>
     </row>
     <row r="289">
@@ -8770,15 +10502,21 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>2</v>
+        <v>1984</v>
       </c>
       <c r="F289" t="n">
+        <v>2</v>
+      </c>
+      <c r="G289" t="n">
         <v>4</v>
       </c>
-      <c r="G289" t="inlineStr">
+      <c r="H289" t="inlineStr">
         <is>
           <t>Paysandu SC</t>
         </is>
+      </c>
+      <c r="I289" t="n">
+        <v>1997</v>
       </c>
     </row>
     <row r="290">
@@ -8799,15 +10537,21 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>1</v>
+        <v>135514</v>
       </c>
       <c r="F290" t="n">
         <v>1</v>
       </c>
-      <c r="G290" t="inlineStr">
+      <c r="G290" t="n">
+        <v>1</v>
+      </c>
+      <c r="H290" t="inlineStr">
         <is>
           <t>Vila Nova FC</t>
         </is>
+      </c>
+      <c r="I290" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="291">
@@ -8828,15 +10572,21 @@
         </is>
       </c>
       <c r="E291" t="n">
+        <v>2012</v>
+      </c>
+      <c r="F291" t="n">
         <v>4</v>
       </c>
-      <c r="F291" t="n">
-        <v>2</v>
-      </c>
-      <c r="G291" t="inlineStr">
+      <c r="G291" t="n">
+        <v>2</v>
+      </c>
+      <c r="H291" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I291" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="292">
@@ -8857,15 +10607,21 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>1</v>
+        <v>1979</v>
       </c>
       <c r="F292" t="n">
-        <v>2</v>
-      </c>
-      <c r="G292" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G292" t="n">
+        <v>2</v>
+      </c>
+      <c r="H292" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I292" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="293">
@@ -8886,15 +10642,21 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>2</v>
+        <v>49202</v>
       </c>
       <c r="F293" t="n">
-        <v>1</v>
-      </c>
-      <c r="G293" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G293" t="n">
+        <v>1</v>
+      </c>
+      <c r="H293" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I293" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="294">
@@ -8915,15 +10677,21 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>1</v>
+        <v>336664</v>
       </c>
       <c r="F294" t="n">
+        <v>1</v>
+      </c>
+      <c r="G294" t="n">
         <v>3</v>
       </c>
-      <c r="G294" t="inlineStr">
+      <c r="H294" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
+      </c>
+      <c r="I294" t="n">
+        <v>21845</v>
       </c>
     </row>
     <row r="295">
@@ -8944,15 +10712,21 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>2</v>
+        <v>1973</v>
       </c>
       <c r="F295" t="n">
-        <v>1</v>
-      </c>
-      <c r="G295" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G295" t="n">
+        <v>1</v>
+      </c>
+      <c r="H295" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
+      </c>
+      <c r="I295" t="n">
+        <v>6982</v>
       </c>
     </row>
     <row r="296">
@@ -8973,15 +10747,21 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>0</v>
+        <v>7315</v>
       </c>
       <c r="F296" t="n">
-        <v>2</v>
-      </c>
-      <c r="G296" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G296" t="n">
+        <v>2</v>
+      </c>
+      <c r="H296" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
+      </c>
+      <c r="I296" t="n">
+        <v>1982</v>
       </c>
     </row>
     <row r="297">
@@ -9002,15 +10782,21 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>0</v>
+        <v>1960</v>
       </c>
       <c r="F297" t="n">
         <v>0</v>
       </c>
-      <c r="G297" t="inlineStr">
+      <c r="G297" t="n">
+        <v>0</v>
+      </c>
+      <c r="H297" t="inlineStr">
         <is>
           <t>Atlético Goianiense</t>
         </is>
+      </c>
+      <c r="I297" t="n">
+        <v>7314</v>
       </c>
     </row>
     <row r="298">
@@ -9031,15 +10817,21 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>1</v>
+        <v>1997</v>
       </c>
       <c r="F298" t="n">
         <v>1</v>
       </c>
-      <c r="G298" t="inlineStr">
+      <c r="G298" t="n">
+        <v>1</v>
+      </c>
+      <c r="H298" t="inlineStr">
         <is>
           <t>Cuiabá</t>
         </is>
+      </c>
+      <c r="I298" t="n">
+        <v>49202</v>
       </c>
     </row>
     <row r="299">
@@ -9060,15 +10852,21 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>1</v>
+        <v>2021</v>
       </c>
       <c r="F299" t="n">
         <v>1</v>
       </c>
-      <c r="G299" t="inlineStr">
+      <c r="G299" t="n">
+        <v>1</v>
+      </c>
+      <c r="H299" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I299" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="300">
@@ -9089,15 +10887,21 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>2</v>
+        <v>342775</v>
       </c>
       <c r="F300" t="n">
         <v>2</v>
       </c>
-      <c r="G300" t="inlineStr">
+      <c r="G300" t="n">
+        <v>2</v>
+      </c>
+      <c r="H300" t="inlineStr">
         <is>
           <t>Amazonas FC</t>
         </is>
+      </c>
+      <c r="I300" t="n">
+        <v>336664</v>
       </c>
     </row>
     <row r="301">
@@ -9118,15 +10922,21 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>2</v>
+        <v>1982</v>
       </c>
       <c r="F301" t="n">
-        <v>0</v>
-      </c>
-      <c r="G301" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G301" t="n">
+        <v>0</v>
+      </c>
+      <c r="H301" t="inlineStr">
         <is>
           <t>Botafogo-SP</t>
         </is>
+      </c>
+      <c r="I301" t="n">
+        <v>1979</v>
       </c>
     </row>
     <row r="302">
@@ -9147,15 +10957,21 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>1</v>
+        <v>22032</v>
       </c>
       <c r="F302" t="n">
-        <v>0</v>
-      </c>
-      <c r="G302" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G302" t="n">
+        <v>0</v>
+      </c>
+      <c r="H302" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
+      </c>
+      <c r="I302" t="n">
+        <v>7315</v>
       </c>
     </row>
     <row r="303">
@@ -9176,15 +10992,21 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>1</v>
+        <v>21845</v>
       </c>
       <c r="F303" t="n">
-        <v>0</v>
-      </c>
-      <c r="G303" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G303" t="n">
+        <v>0</v>
+      </c>
+      <c r="H303" t="inlineStr">
         <is>
           <t>Grêmio Novorizontino</t>
         </is>
+      </c>
+      <c r="I303" t="n">
+        <v>135514</v>
       </c>
     </row>
     <row r="304">
@@ -9205,15 +11027,21 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>0</v>
+        <v>6982</v>
       </c>
       <c r="F304" t="n">
         <v>0</v>
       </c>
-      <c r="G304" t="inlineStr">
+      <c r="G304" t="n">
+        <v>0</v>
+      </c>
+      <c r="H304" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
+      </c>
+      <c r="I304" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="305">
@@ -9234,15 +11062,21 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>1</v>
+        <v>35285</v>
       </c>
       <c r="F305" t="n">
+        <v>1</v>
+      </c>
+      <c r="G305" t="n">
         <v>3</v>
       </c>
-      <c r="G305" t="inlineStr">
+      <c r="H305" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
+      </c>
+      <c r="I305" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="306">
@@ -9263,15 +11097,21 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>0</v>
+        <v>39634</v>
       </c>
       <c r="F306" t="n">
-        <v>1</v>
-      </c>
-      <c r="G306" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G306" t="n">
+        <v>1</v>
+      </c>
+      <c r="H306" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I306" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="307">
@@ -9292,15 +11132,21 @@
         </is>
       </c>
       <c r="E307" t="n">
+        <v>7314</v>
+      </c>
+      <c r="F307" t="n">
         <v>3</v>
       </c>
-      <c r="F307" t="n">
-        <v>0</v>
-      </c>
-      <c r="G307" t="inlineStr">
+      <c r="G307" t="n">
+        <v>0</v>
+      </c>
+      <c r="H307" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I307" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="308">
@@ -9321,15 +11167,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>2</v>
+        <v>336664</v>
       </c>
       <c r="F308" t="n">
-        <v>1</v>
-      </c>
-      <c r="G308" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G308" t="n">
+        <v>1</v>
+      </c>
+      <c r="H308" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I308" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="309">
@@ -9350,15 +11202,21 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>1</v>
+        <v>1960</v>
       </c>
       <c r="F309" t="n">
-        <v>2</v>
-      </c>
-      <c r="G309" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G309" t="n">
+        <v>2</v>
+      </c>
+      <c r="H309" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I309" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="310">
@@ -9379,15 +11237,21 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>1</v>
+        <v>1979</v>
       </c>
       <c r="F310" t="n">
-        <v>0</v>
-      </c>
-      <c r="G310" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G310" t="n">
+        <v>0</v>
+      </c>
+      <c r="H310" t="inlineStr">
         <is>
           <t>Paysandu SC</t>
         </is>
+      </c>
+      <c r="I310" t="n">
+        <v>1997</v>
       </c>
     </row>
     <row r="311">
@@ -9408,15 +11272,21 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>0</v>
+        <v>49202</v>
       </c>
       <c r="F311" t="n">
-        <v>1</v>
-      </c>
-      <c r="G311" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G311" t="n">
+        <v>1</v>
+      </c>
+      <c r="H311" t="inlineStr">
         <is>
           <t>Grêmio Novorizontino</t>
         </is>
+      </c>
+      <c r="I311" t="n">
+        <v>135514</v>
       </c>
     </row>
     <row r="312">
@@ -9437,15 +11307,21 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>1</v>
+        <v>39634</v>
       </c>
       <c r="F312" t="n">
+        <v>1</v>
+      </c>
+      <c r="G312" t="n">
         <v>4</v>
       </c>
-      <c r="G312" t="inlineStr">
+      <c r="H312" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I312" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="313">
@@ -9466,15 +11342,21 @@
         </is>
       </c>
       <c r="E313" t="n">
+        <v>7315</v>
+      </c>
+      <c r="F313" t="n">
         <v>3</v>
       </c>
-      <c r="F313" t="n">
-        <v>0</v>
-      </c>
-      <c r="G313" t="inlineStr">
+      <c r="G313" t="n">
+        <v>0</v>
+      </c>
+      <c r="H313" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
+      </c>
+      <c r="I313" t="n">
+        <v>6982</v>
       </c>
     </row>
     <row r="314">
@@ -9495,15 +11377,21 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>1</v>
+        <v>1973</v>
       </c>
       <c r="F314" t="n">
         <v>1</v>
       </c>
-      <c r="G314" t="inlineStr">
+      <c r="G314" t="n">
+        <v>1</v>
+      </c>
+      <c r="H314" t="inlineStr">
         <is>
           <t>Vila Nova FC</t>
         </is>
+      </c>
+      <c r="I314" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="315">
@@ -9524,15 +11412,21 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>0</v>
+        <v>35285</v>
       </c>
       <c r="F315" t="n">
-        <v>1</v>
-      </c>
-      <c r="G315" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G315" t="n">
+        <v>1</v>
+      </c>
+      <c r="H315" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
+      </c>
+      <c r="I315" t="n">
+        <v>21845</v>
       </c>
     </row>
     <row r="316">
@@ -9553,15 +11447,21 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>2</v>
+        <v>1982</v>
       </c>
       <c r="F316" t="n">
-        <v>1</v>
-      </c>
-      <c r="G316" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G316" t="n">
+        <v>1</v>
+      </c>
+      <c r="H316" t="inlineStr">
         <is>
           <t>Atlético Goianiense</t>
         </is>
+      </c>
+      <c r="I316" t="n">
+        <v>7314</v>
       </c>
     </row>
     <row r="317">
@@ -9582,15 +11482,21 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>2</v>
+        <v>2012</v>
       </c>
       <c r="F317" t="n">
-        <v>1</v>
-      </c>
-      <c r="G317" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G317" t="n">
+        <v>1</v>
+      </c>
+      <c r="H317" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I317" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="318">
@@ -9611,15 +11517,21 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>1</v>
+        <v>342775</v>
       </c>
       <c r="F318" t="n">
         <v>1</v>
       </c>
-      <c r="G318" t="inlineStr">
+      <c r="G318" t="n">
+        <v>1</v>
+      </c>
+      <c r="H318" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
+      </c>
+      <c r="I318" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="319">
@@ -9640,15 +11552,21 @@
         </is>
       </c>
       <c r="E319" t="n">
+        <v>135514</v>
+      </c>
+      <c r="F319" t="n">
         <v>3</v>
       </c>
-      <c r="F319" t="n">
-        <v>0</v>
-      </c>
-      <c r="G319" t="inlineStr">
+      <c r="G319" t="n">
+        <v>0</v>
+      </c>
+      <c r="H319" t="inlineStr">
         <is>
           <t>Operário-PR</t>
         </is>
+      </c>
+      <c r="I319" t="n">
+        <v>39634</v>
       </c>
     </row>
     <row r="320">
@@ -9669,15 +11587,21 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>2</v>
+        <v>1984</v>
       </c>
       <c r="F320" t="n">
-        <v>1</v>
-      </c>
-      <c r="G320" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G320" t="n">
+        <v>1</v>
+      </c>
+      <c r="H320" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
+      </c>
+      <c r="I320" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="321">
@@ -9698,15 +11622,21 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>1</v>
+        <v>2021</v>
       </c>
       <c r="F321" t="n">
-        <v>0</v>
-      </c>
-      <c r="G321" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G321" t="n">
+        <v>0</v>
+      </c>
+      <c r="H321" t="inlineStr">
         <is>
           <t>Amazonas FC</t>
         </is>
+      </c>
+      <c r="I321" t="n">
+        <v>336664</v>
       </c>
     </row>
     <row r="322">
@@ -9727,15 +11657,21 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>1</v>
+        <v>49202</v>
       </c>
       <c r="F322" t="n">
-        <v>0</v>
-      </c>
-      <c r="G322" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G322" t="n">
+        <v>0</v>
+      </c>
+      <c r="H322" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
+      </c>
+      <c r="I322" t="n">
+        <v>1982</v>
       </c>
     </row>
     <row r="323">
@@ -9756,15 +11692,21 @@
         </is>
       </c>
       <c r="E323" t="n">
+        <v>6982</v>
+      </c>
+      <c r="F323" t="n">
         <v>3</v>
       </c>
-      <c r="F323" t="n">
-        <v>0</v>
-      </c>
-      <c r="G323" t="inlineStr">
+      <c r="G323" t="n">
+        <v>0</v>
+      </c>
+      <c r="H323" t="inlineStr">
         <is>
           <t>Atlético Goianiense</t>
         </is>
+      </c>
+      <c r="I323" t="n">
+        <v>7314</v>
       </c>
     </row>
     <row r="324">
@@ -9785,15 +11727,21 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>2</v>
+        <v>22032</v>
       </c>
       <c r="F324" t="n">
         <v>2</v>
       </c>
-      <c r="G324" t="inlineStr">
+      <c r="G324" t="n">
+        <v>2</v>
+      </c>
+      <c r="H324" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I324" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="325">
@@ -9814,15 +11762,21 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>1</v>
+        <v>21845</v>
       </c>
       <c r="F325" t="n">
         <v>1</v>
       </c>
-      <c r="G325" t="inlineStr">
+      <c r="G325" t="n">
+        <v>1</v>
+      </c>
+      <c r="H325" t="inlineStr">
         <is>
           <t>Botafogo-SP</t>
         </is>
+      </c>
+      <c r="I325" t="n">
+        <v>1979</v>
       </c>
     </row>
     <row r="326">
@@ -9843,15 +11797,21 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>2</v>
+        <v>1997</v>
       </c>
       <c r="F326" t="n">
+        <v>2</v>
+      </c>
+      <c r="G326" t="n">
         <v>3</v>
       </c>
-      <c r="G326" t="inlineStr">
+      <c r="H326" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I326" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="327">
@@ -9872,15 +11832,21 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>1</v>
+        <v>1967</v>
       </c>
       <c r="F327" t="n">
         <v>1</v>
       </c>
-      <c r="G327" t="inlineStr">
+      <c r="G327" t="n">
+        <v>1</v>
+      </c>
+      <c r="H327" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
+      </c>
+      <c r="I327" t="n">
+        <v>7315</v>
       </c>
     </row>
     <row r="328">
@@ -9901,15 +11867,21 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>0</v>
+        <v>336664</v>
       </c>
       <c r="F328" t="n">
         <v>0</v>
       </c>
-      <c r="G328" t="inlineStr">
+      <c r="G328" t="n">
+        <v>0</v>
+      </c>
+      <c r="H328" t="inlineStr">
         <is>
           <t>Grêmio Novorizontino</t>
         </is>
+      </c>
+      <c r="I328" t="n">
+        <v>135514</v>
       </c>
     </row>
     <row r="329">
@@ -9930,15 +11902,21 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>1</v>
+        <v>7314</v>
       </c>
       <c r="F329" t="n">
-        <v>0</v>
-      </c>
-      <c r="G329" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G329" t="n">
+        <v>0</v>
+      </c>
+      <c r="H329" t="inlineStr">
         <is>
           <t>Vila Nova FC</t>
         </is>
+      </c>
+      <c r="I329" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="330">
@@ -9959,15 +11937,21 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>1</v>
+        <v>1973</v>
       </c>
       <c r="F330" t="n">
         <v>1</v>
       </c>
-      <c r="G330" t="inlineStr">
+      <c r="G330" t="n">
+        <v>1</v>
+      </c>
+      <c r="H330" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I330" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="331">
@@ -9988,15 +11972,21 @@
         </is>
       </c>
       <c r="E331" t="n">
+        <v>2012</v>
+      </c>
+      <c r="F331" t="n">
         <v>3</v>
       </c>
-      <c r="F331" t="n">
-        <v>1</v>
-      </c>
-      <c r="G331" t="inlineStr">
+      <c r="G331" t="n">
+        <v>1</v>
+      </c>
+      <c r="H331" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I331" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="332">
@@ -10017,15 +12007,21 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>1</v>
+        <v>7315</v>
       </c>
       <c r="F332" t="n">
         <v>1</v>
       </c>
-      <c r="G332" t="inlineStr">
+      <c r="G332" t="n">
+        <v>1</v>
+      </c>
+      <c r="H332" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I332" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="333">
@@ -10046,15 +12042,21 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>2</v>
+        <v>39634</v>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
-      </c>
-      <c r="G333" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G333" t="n">
+        <v>1</v>
+      </c>
+      <c r="H333" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
+      </c>
+      <c r="I333" t="n">
+        <v>6982</v>
       </c>
     </row>
     <row r="334">
@@ -10075,15 +12077,21 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>2</v>
+        <v>1979</v>
       </c>
       <c r="F334" t="n">
         <v>2</v>
       </c>
-      <c r="G334" t="inlineStr">
+      <c r="G334" t="n">
+        <v>2</v>
+      </c>
+      <c r="H334" t="inlineStr">
         <is>
           <t>Cuiabá</t>
         </is>
+      </c>
+      <c r="I334" t="n">
+        <v>49202</v>
       </c>
     </row>
     <row r="335">
@@ -10104,15 +12112,21 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>0</v>
+        <v>1982</v>
       </c>
       <c r="F335" t="n">
         <v>0</v>
       </c>
-      <c r="G335" t="inlineStr">
+      <c r="G335" t="n">
+        <v>0</v>
+      </c>
+      <c r="H335" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I335" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="336">
@@ -10133,15 +12147,21 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>1</v>
+        <v>1960</v>
       </c>
       <c r="F336" t="n">
+        <v>1</v>
+      </c>
+      <c r="G336" t="n">
         <v>3</v>
       </c>
-      <c r="G336" t="inlineStr">
+      <c r="H336" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
+      </c>
+      <c r="I336" t="n">
+        <v>21845</v>
       </c>
     </row>
     <row r="337">
@@ -10162,15 +12182,21 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>2</v>
+        <v>35285</v>
       </c>
       <c r="F337" t="n">
         <v>2</v>
       </c>
-      <c r="G337" t="inlineStr">
+      <c r="G337" t="n">
+        <v>2</v>
+      </c>
+      <c r="H337" t="inlineStr">
         <is>
           <t>Paysandu SC</t>
         </is>
+      </c>
+      <c r="I337" t="n">
+        <v>1997</v>
       </c>
     </row>
     <row r="338">
@@ -10191,15 +12217,21 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>1</v>
+        <v>135514</v>
       </c>
       <c r="F338" t="n">
         <v>1</v>
       </c>
-      <c r="G338" t="inlineStr">
+      <c r="G338" t="n">
+        <v>1</v>
+      </c>
+      <c r="H338" t="inlineStr">
         <is>
           <t>Botafogo-SP</t>
         </is>
+      </c>
+      <c r="I338" t="n">
+        <v>1979</v>
       </c>
     </row>
     <row r="339">
@@ -10220,15 +12252,21 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>1</v>
+        <v>49202</v>
       </c>
       <c r="F339" t="n">
+        <v>1</v>
+      </c>
+      <c r="G339" t="n">
         <v>3</v>
       </c>
-      <c r="G339" t="inlineStr">
+      <c r="H339" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I339" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="340">
@@ -10249,15 +12287,21 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>0</v>
+        <v>342775</v>
       </c>
       <c r="F340" t="n">
-        <v>2</v>
-      </c>
-      <c r="G340" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G340" t="n">
+        <v>2</v>
+      </c>
+      <c r="H340" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
+      </c>
+      <c r="I340" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="341">
@@ -10278,15 +12322,21 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>0</v>
+        <v>6982</v>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
-      </c>
-      <c r="G341" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G341" t="n">
+        <v>1</v>
+      </c>
+      <c r="H341" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
+      </c>
+      <c r="I341" t="n">
+        <v>1982</v>
       </c>
     </row>
     <row r="342">
@@ -10307,15 +12357,21 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>1</v>
+        <v>1997</v>
       </c>
       <c r="F342" t="n">
-        <v>2</v>
-      </c>
-      <c r="G342" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G342" t="n">
+        <v>2</v>
+      </c>
+      <c r="H342" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
+      </c>
+      <c r="I342" t="n">
+        <v>7315</v>
       </c>
     </row>
     <row r="343">
@@ -10336,15 +12392,21 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>1</v>
+        <v>1984</v>
       </c>
       <c r="F343" t="n">
-        <v>2</v>
-      </c>
-      <c r="G343" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G343" t="n">
+        <v>2</v>
+      </c>
+      <c r="H343" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
+      </c>
+      <c r="I343" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="344">
@@ -10365,15 +12427,21 @@
         </is>
       </c>
       <c r="E344" t="n">
-        <v>2</v>
+        <v>22032</v>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
-      </c>
-      <c r="G344" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G344" t="n">
+        <v>1</v>
+      </c>
+      <c r="H344" t="inlineStr">
         <is>
           <t>Atlético Goianiense</t>
         </is>
+      </c>
+      <c r="I344" t="n">
+        <v>7314</v>
       </c>
     </row>
     <row r="345">
@@ -10394,15 +12462,21 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>2</v>
+        <v>2021</v>
       </c>
       <c r="F345" t="n">
         <v>2</v>
       </c>
-      <c r="G345" t="inlineStr">
+      <c r="G345" t="n">
+        <v>2</v>
+      </c>
+      <c r="H345" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I345" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="346">
@@ -10423,15 +12497,21 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>2</v>
+        <v>21845</v>
       </c>
       <c r="F346" t="n">
-        <v>0</v>
-      </c>
-      <c r="G346" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G346" t="n">
+        <v>0</v>
+      </c>
+      <c r="H346" t="inlineStr">
         <is>
           <t>Operário-PR</t>
         </is>
+      </c>
+      <c r="I346" t="n">
+        <v>39634</v>
       </c>
     </row>
     <row r="347">
@@ -10452,15 +12532,21 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>2</v>
+        <v>1967</v>
       </c>
       <c r="F347" t="n">
-        <v>0</v>
-      </c>
-      <c r="G347" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G347" t="n">
+        <v>0</v>
+      </c>
+      <c r="H347" t="inlineStr">
         <is>
           <t>Amazonas FC</t>
         </is>
+      </c>
+      <c r="I347" t="n">
+        <v>336664</v>
       </c>
     </row>
     <row r="348">
@@ -10481,15 +12567,21 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>2</v>
+        <v>7314</v>
       </c>
       <c r="F348" t="n">
-        <v>1</v>
-      </c>
-      <c r="G348" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G348" t="n">
+        <v>1</v>
+      </c>
+      <c r="H348" t="inlineStr">
         <is>
           <t>Paysandu SC</t>
         </is>
+      </c>
+      <c r="I348" t="n">
+        <v>1997</v>
       </c>
     </row>
     <row r="349">
@@ -10510,15 +12602,21 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>0</v>
+        <v>1982</v>
       </c>
       <c r="F349" t="n">
         <v>0</v>
       </c>
-      <c r="G349" t="inlineStr">
+      <c r="G349" t="n">
+        <v>0</v>
+      </c>
+      <c r="H349" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I349" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="350">
@@ -10539,15 +12637,21 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>0</v>
+        <v>35285</v>
       </c>
       <c r="F350" t="n">
         <v>0</v>
       </c>
-      <c r="G350" t="inlineStr">
+      <c r="G350" t="n">
+        <v>0</v>
+      </c>
+      <c r="H350" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I350" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="351">
@@ -10568,15 +12672,21 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>0</v>
+        <v>1960</v>
       </c>
       <c r="F351" t="n">
-        <v>1</v>
-      </c>
-      <c r="G351" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G351" t="n">
+        <v>1</v>
+      </c>
+      <c r="H351" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I351" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="352">
@@ -10597,15 +12707,21 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>2</v>
+        <v>7315</v>
       </c>
       <c r="F352" t="n">
-        <v>1</v>
-      </c>
-      <c r="G352" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G352" t="n">
+        <v>1</v>
+      </c>
+      <c r="H352" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I352" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="353">
@@ -10626,15 +12742,21 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>2</v>
+        <v>336664</v>
       </c>
       <c r="F353" t="n">
-        <v>0</v>
-      </c>
-      <c r="G353" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G353" t="n">
+        <v>0</v>
+      </c>
+      <c r="H353" t="inlineStr">
         <is>
           <t>Cuiabá</t>
         </is>
+      </c>
+      <c r="I353" t="n">
+        <v>49202</v>
       </c>
     </row>
     <row r="354">
@@ -10655,15 +12777,21 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>1</v>
+        <v>2012</v>
       </c>
       <c r="F354" t="n">
         <v>1</v>
       </c>
-      <c r="G354" t="inlineStr">
+      <c r="G354" t="n">
+        <v>1</v>
+      </c>
+      <c r="H354" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
+      </c>
+      <c r="I354" t="n">
+        <v>21845</v>
       </c>
     </row>
     <row r="355">
@@ -10684,15 +12812,21 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>2</v>
+        <v>39634</v>
       </c>
       <c r="F355" t="n">
         <v>2</v>
       </c>
-      <c r="G355" t="inlineStr">
+      <c r="G355" t="n">
+        <v>2</v>
+      </c>
+      <c r="H355" t="inlineStr">
         <is>
           <t>Vila Nova FC</t>
         </is>
+      </c>
+      <c r="I355" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="356">
@@ -10713,15 +12847,21 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>2</v>
+        <v>1973</v>
       </c>
       <c r="F356" t="n">
         <v>2</v>
       </c>
-      <c r="G356" t="inlineStr">
+      <c r="G356" t="n">
+        <v>2</v>
+      </c>
+      <c r="H356" t="inlineStr">
         <is>
           <t>Grêmio Novorizontino</t>
         </is>
+      </c>
+      <c r="I356" t="n">
+        <v>135514</v>
       </c>
     </row>
     <row r="357">
@@ -10742,15 +12882,21 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>0</v>
+        <v>6982</v>
       </c>
       <c r="F357" t="n">
-        <v>1</v>
-      </c>
-      <c r="G357" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G357" t="n">
+        <v>1</v>
+      </c>
+      <c r="H357" t="inlineStr">
         <is>
           <t>Botafogo-SP</t>
         </is>
+      </c>
+      <c r="I357" t="n">
+        <v>1979</v>
       </c>
     </row>
     <row r="358">
@@ -10771,15 +12917,21 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>2</v>
+        <v>342775</v>
       </c>
       <c r="F358" t="n">
-        <v>1</v>
-      </c>
-      <c r="G358" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G358" t="n">
+        <v>1</v>
+      </c>
+      <c r="H358" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I358" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="359">
@@ -10800,15 +12952,21 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>0</v>
+        <v>49202</v>
       </c>
       <c r="F359" t="n">
-        <v>1</v>
-      </c>
-      <c r="G359" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G359" t="n">
+        <v>1</v>
+      </c>
+      <c r="H359" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
+      </c>
+      <c r="I359" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="360">
@@ -10829,15 +12987,21 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>1</v>
+        <v>135514</v>
       </c>
       <c r="F360" t="n">
         <v>1</v>
       </c>
-      <c r="G360" t="inlineStr">
+      <c r="G360" t="n">
+        <v>1</v>
+      </c>
+      <c r="H360" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I360" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="361">
@@ -10858,15 +13022,21 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>2</v>
+        <v>1967</v>
       </c>
       <c r="F361" t="n">
-        <v>0</v>
-      </c>
-      <c r="G361" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G361" t="n">
+        <v>0</v>
+      </c>
+      <c r="H361" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
+      </c>
+      <c r="I361" t="n">
+        <v>6982</v>
       </c>
     </row>
     <row r="362">
@@ -10887,15 +13057,21 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>2</v>
+        <v>2021</v>
       </c>
       <c r="F362" t="n">
         <v>2</v>
       </c>
-      <c r="G362" t="inlineStr">
+      <c r="G362" t="n">
+        <v>2</v>
+      </c>
+      <c r="H362" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
+      </c>
+      <c r="I362" t="n">
+        <v>7315</v>
       </c>
     </row>
     <row r="363">
@@ -10916,15 +13092,21 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>1</v>
+        <v>1984</v>
       </c>
       <c r="F363" t="n">
-        <v>0</v>
-      </c>
-      <c r="G363" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G363" t="n">
+        <v>0</v>
+      </c>
+      <c r="H363" t="inlineStr">
         <is>
           <t>Atlético Goianiense</t>
         </is>
+      </c>
+      <c r="I363" t="n">
+        <v>7314</v>
       </c>
     </row>
     <row r="364">
@@ -10945,15 +13127,21 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>2</v>
+        <v>22032</v>
       </c>
       <c r="F364" t="n">
         <v>2</v>
       </c>
-      <c r="G364" t="inlineStr">
+      <c r="G364" t="n">
+        <v>2</v>
+      </c>
+      <c r="H364" t="inlineStr">
         <is>
           <t>Operário-PR</t>
         </is>
+      </c>
+      <c r="I364" t="n">
+        <v>39634</v>
       </c>
     </row>
     <row r="365">
@@ -10974,15 +13162,21 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>1</v>
+        <v>1997</v>
       </c>
       <c r="F365" t="n">
-        <v>2</v>
-      </c>
-      <c r="G365" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G365" t="n">
+        <v>2</v>
+      </c>
+      <c r="H365" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
+      </c>
+      <c r="I365" t="n">
+        <v>1982</v>
       </c>
     </row>
     <row r="366">
@@ -11003,15 +13197,21 @@
         </is>
       </c>
       <c r="E366" t="n">
-        <v>1</v>
+        <v>1979</v>
       </c>
       <c r="F366" t="n">
-        <v>0</v>
-      </c>
-      <c r="G366" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G366" t="n">
+        <v>0</v>
+      </c>
+      <c r="H366" t="inlineStr">
         <is>
           <t>Amazonas FC</t>
         </is>
+      </c>
+      <c r="I366" t="n">
+        <v>336664</v>
       </c>
     </row>
     <row r="367">
@@ -11032,15 +13232,21 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>0</v>
+        <v>21845</v>
       </c>
       <c r="F367" t="n">
-        <v>1</v>
-      </c>
-      <c r="G367" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G367" t="n">
+        <v>1</v>
+      </c>
+      <c r="H367" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
+      </c>
+      <c r="I367" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="368">
@@ -11061,15 +13267,21 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>2</v>
+        <v>1997</v>
       </c>
       <c r="F368" t="n">
         <v>2</v>
       </c>
-      <c r="G368" t="inlineStr">
+      <c r="G368" t="n">
+        <v>2</v>
+      </c>
+      <c r="H368" t="inlineStr">
         <is>
           <t>Amazonas FC</t>
         </is>
+      </c>
+      <c r="I368" t="n">
+        <v>336664</v>
       </c>
     </row>
     <row r="369">
@@ -11090,15 +13302,21 @@
         </is>
       </c>
       <c r="E369" t="n">
-        <v>0</v>
+        <v>7314</v>
       </c>
       <c r="F369" t="n">
         <v>0</v>
       </c>
-      <c r="G369" t="inlineStr">
+      <c r="G369" t="n">
+        <v>0</v>
+      </c>
+      <c r="H369" t="inlineStr">
         <is>
           <t>Operário-PR</t>
         </is>
+      </c>
+      <c r="I369" t="n">
+        <v>39634</v>
       </c>
     </row>
     <row r="370">
@@ -11119,15 +13337,21 @@
         </is>
       </c>
       <c r="E370" t="n">
+        <v>7315</v>
+      </c>
+      <c r="F370" t="n">
         <v>3</v>
       </c>
-      <c r="F370" t="n">
-        <v>1</v>
-      </c>
-      <c r="G370" t="inlineStr">
+      <c r="G370" t="n">
+        <v>1</v>
+      </c>
+      <c r="H370" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
+      </c>
+      <c r="I370" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="371">
@@ -11148,15 +13372,21 @@
         </is>
       </c>
       <c r="E371" t="n">
-        <v>2</v>
+        <v>22032</v>
       </c>
       <c r="F371" t="n">
-        <v>0</v>
-      </c>
-      <c r="G371" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G371" t="n">
+        <v>0</v>
+      </c>
+      <c r="H371" t="inlineStr">
         <is>
           <t>Vila Nova FC</t>
         </is>
+      </c>
+      <c r="I371" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="372">
@@ -11177,15 +13407,21 @@
         </is>
       </c>
       <c r="E372" t="n">
-        <v>0</v>
+        <v>1982</v>
       </c>
       <c r="F372" t="n">
         <v>0</v>
       </c>
-      <c r="G372" t="inlineStr">
+      <c r="G372" t="n">
+        <v>0</v>
+      </c>
+      <c r="H372" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
+      </c>
+      <c r="I372" t="n">
+        <v>342775</v>
       </c>
     </row>
     <row r="373">
@@ -11206,15 +13442,21 @@
         </is>
       </c>
       <c r="E373" t="n">
-        <v>1</v>
+        <v>6982</v>
       </c>
       <c r="F373" t="n">
         <v>1</v>
       </c>
-      <c r="G373" t="inlineStr">
+      <c r="G373" t="n">
+        <v>1</v>
+      </c>
+      <c r="H373" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
+      </c>
+      <c r="I373" t="n">
+        <v>21845</v>
       </c>
     </row>
     <row r="374">
@@ -11235,15 +13477,21 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>1</v>
+        <v>1973</v>
       </c>
       <c r="F374" t="n">
         <v>1</v>
       </c>
-      <c r="G374" t="inlineStr">
+      <c r="G374" t="n">
+        <v>1</v>
+      </c>
+      <c r="H374" t="inlineStr">
         <is>
           <t>Cuiabá</t>
         </is>
+      </c>
+      <c r="I374" t="n">
+        <v>49202</v>
       </c>
     </row>
     <row r="375">
@@ -11264,15 +13512,21 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>2</v>
+        <v>1984</v>
       </c>
       <c r="F375" t="n">
-        <v>0</v>
-      </c>
-      <c r="G375" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G375" t="n">
+        <v>0</v>
+      </c>
+      <c r="H375" t="inlineStr">
         <is>
           <t>Botafogo-SP</t>
         </is>
+      </c>
+      <c r="I375" t="n">
+        <v>1979</v>
       </c>
     </row>
     <row r="376">
@@ -11293,15 +13547,21 @@
         </is>
       </c>
       <c r="E376" t="n">
-        <v>1</v>
+        <v>35285</v>
       </c>
       <c r="F376" t="n">
-        <v>2</v>
-      </c>
-      <c r="G376" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G376" t="n">
+        <v>2</v>
+      </c>
+      <c r="H376" t="inlineStr">
         <is>
           <t>Athletico</t>
         </is>
+      </c>
+      <c r="I376" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="377">
@@ -11322,15 +13582,21 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>1</v>
+        <v>1960</v>
       </c>
       <c r="F377" t="n">
-        <v>0</v>
-      </c>
-      <c r="G377" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G377" t="n">
+        <v>0</v>
+      </c>
+      <c r="H377" t="inlineStr">
         <is>
           <t>Grêmio Novorizontino</t>
         </is>
+      </c>
+      <c r="I377" t="n">
+        <v>135514</v>
       </c>
     </row>
     <row r="378">
@@ -11351,15 +13617,21 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>2</v>
+        <v>2021</v>
       </c>
       <c r="F378" t="n">
         <v>2</v>
       </c>
-      <c r="G378" t="inlineStr">
+      <c r="G378" t="n">
+        <v>2</v>
+      </c>
+      <c r="H378" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
+      </c>
+      <c r="I378" t="n">
+        <v>6982</v>
       </c>
     </row>
     <row r="379">
@@ -11380,15 +13652,21 @@
         </is>
       </c>
       <c r="E379" t="n">
+        <v>135514</v>
+      </c>
+      <c r="F379" t="n">
         <v>3</v>
       </c>
-      <c r="F379" t="n">
-        <v>0</v>
-      </c>
-      <c r="G379" t="inlineStr">
+      <c r="G379" t="n">
+        <v>0</v>
+      </c>
+      <c r="H379" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
+      </c>
+      <c r="I379" t="n">
+        <v>22032</v>
       </c>
     </row>
     <row r="380">
@@ -11409,15 +13687,21 @@
         </is>
       </c>
       <c r="E380" t="n">
-        <v>1</v>
+        <v>336664</v>
       </c>
       <c r="F380" t="n">
-        <v>2</v>
-      </c>
-      <c r="G380" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G380" t="n">
+        <v>2</v>
+      </c>
+      <c r="H380" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
+      </c>
+      <c r="I380" t="n">
+        <v>1982</v>
       </c>
     </row>
     <row r="381">
@@ -11438,15 +13722,21 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>2</v>
+        <v>342775</v>
       </c>
       <c r="F381" t="n">
-        <v>1</v>
-      </c>
-      <c r="G381" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G381" t="n">
+        <v>1</v>
+      </c>
+      <c r="H381" t="inlineStr">
         <is>
           <t>Paysandu SC</t>
         </is>
+      </c>
+      <c r="I381" t="n">
+        <v>1997</v>
       </c>
     </row>
     <row r="382">
@@ -11467,15 +13757,21 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>1</v>
+        <v>1967</v>
       </c>
       <c r="F382" t="n">
-        <v>0</v>
-      </c>
-      <c r="G382" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G382" t="n">
+        <v>0</v>
+      </c>
+      <c r="H382" t="inlineStr">
         <is>
           <t>América Mineiro</t>
         </is>
+      </c>
+      <c r="I382" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="383">
@@ -11496,15 +13792,21 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>0</v>
+        <v>1979</v>
       </c>
       <c r="F383" t="n">
         <v>0</v>
       </c>
-      <c r="G383" t="inlineStr">
+      <c r="G383" t="n">
+        <v>0</v>
+      </c>
+      <c r="H383" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
+      </c>
+      <c r="I383" t="n">
+        <v>7315</v>
       </c>
     </row>
     <row r="384">
@@ -11525,15 +13827,21 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>1</v>
+        <v>21845</v>
       </c>
       <c r="F384" t="n">
-        <v>0</v>
-      </c>
-      <c r="G384" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G384" t="n">
+        <v>0</v>
+      </c>
+      <c r="H384" t="inlineStr">
         <is>
           <t>Atlético Goianiense</t>
         </is>
+      </c>
+      <c r="I384" t="n">
+        <v>7314</v>
       </c>
     </row>
     <row r="385">
@@ -11554,15 +13862,21 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>1</v>
+        <v>49202</v>
       </c>
       <c r="F385" t="n">
-        <v>0</v>
-      </c>
-      <c r="G385" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G385" t="n">
+        <v>0</v>
+      </c>
+      <c r="H385" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
+      </c>
+      <c r="I385" t="n">
+        <v>1984</v>
       </c>
     </row>
     <row r="386">
@@ -11583,15 +13897,21 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>2</v>
+        <v>39634</v>
       </c>
       <c r="F386" t="n">
-        <v>1</v>
-      </c>
-      <c r="G386" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G386" t="n">
+        <v>1</v>
+      </c>
+      <c r="H386" t="inlineStr">
         <is>
           <t>Ferroviária</t>
         </is>
+      </c>
+      <c r="I386" t="n">
+        <v>35285</v>
       </c>
     </row>
     <row r="387">
@@ -11612,15 +13932,21 @@
         </is>
       </c>
       <c r="E387" t="n">
+        <v>2012</v>
+      </c>
+      <c r="F387" t="n">
         <v>3</v>
       </c>
-      <c r="F387" t="n">
-        <v>1</v>
-      </c>
-      <c r="G387" t="inlineStr">
+      <c r="G387" t="n">
+        <v>1</v>
+      </c>
+      <c r="H387" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
+      </c>
+      <c r="I387" t="n">
+        <v>1960</v>
       </c>
     </row>
   </sheetData>
